--- a/textbook_examples/sask_rm_yields_2024_2025.xlsx
+++ b/textbook_examples/sask_rm_yields_2024_2025.xlsx
@@ -444,7 +444,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J591"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
@@ -458,7 +458,7 @@
     <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Year</t>
@@ -510,7 +510,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1">
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="n">
         <v>2024</v>
       </c>
@@ -533,7 +533,7 @@
         <v>40.1</v>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>2025</v>
       </c>
@@ -559,7 +559,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1">
+    <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="n">
         <v>2024</v>
       </c>
@@ -591,7 +591,7 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
+    <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>2025</v>
       </c>
@@ -620,7 +620,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1">
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="n">
         <v>2024</v>
       </c>
@@ -652,7 +652,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
+    <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>2025</v>
       </c>
@@ -684,7 +684,7 @@
         <v>28.6</v>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1">
+    <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="n">
         <v>2024</v>
       </c>
@@ -716,7 +716,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1">
+    <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>2025</v>
       </c>
@@ -748,7 +748,7 @@
         <v>31.6</v>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1">
+    <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="n">
         <v>2024</v>
       </c>
@@ -777,7 +777,7 @@
         <v>18.4</v>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
+    <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>2025</v>
       </c>
@@ -806,7 +806,7 @@
         <v>31.3</v>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1">
+    <row r="12" ht="18" customHeight="1">
       <c r="A12" s="3" t="n">
         <v>2024</v>
       </c>
@@ -838,7 +838,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1">
+    <row r="13" ht="18" customHeight="1">
       <c r="A13" s="3" t="n">
         <v>2025</v>
       </c>
@@ -867,7 +867,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1">
+    <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="n">
         <v>2024</v>
       </c>
@@ -890,7 +890,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1">
+    <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="n">
         <v>2025</v>
       </c>
@@ -916,7 +916,7 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1">
+    <row r="16" ht="18" customHeight="1">
       <c r="A16" s="3" t="n">
         <v>2024</v>
       </c>
@@ -945,7 +945,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="17" ht="16" customHeight="1">
+    <row r="17" ht="18" customHeight="1">
       <c r="A17" s="3" t="n">
         <v>2025</v>
       </c>
@@ -977,7 +977,7 @@
         <v>30.2</v>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1">
+    <row r="18" ht="18" customHeight="1">
       <c r="A18" s="3" t="n">
         <v>2024</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1">
+    <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="n">
         <v>2025</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>31.3</v>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1">
+    <row r="20" ht="18" customHeight="1">
       <c r="A20" s="3" t="n">
         <v>2024</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1">
+    <row r="21" ht="18" customHeight="1">
       <c r="A21" s="3" t="n">
         <v>2025</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="22" ht="16" customHeight="1">
+    <row r="22" ht="18" customHeight="1">
       <c r="A22" s="3" t="n">
         <v>2024</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1">
+    <row r="23" ht="18" customHeight="1">
       <c r="A23" s="3" t="n">
         <v>2025</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1">
+    <row r="24" ht="18" customHeight="1">
       <c r="A24" s="3" t="n">
         <v>2024</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="25" ht="16" customHeight="1">
+    <row r="25" ht="18" customHeight="1">
       <c r="A25" s="3" t="n">
         <v>2025</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1">
+    <row r="26" ht="18" customHeight="1">
       <c r="A26" s="3" t="n">
         <v>2024</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="27" ht="16" customHeight="1">
+    <row r="27" ht="18" customHeight="1">
       <c r="A27" s="3" t="n">
         <v>2025</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>29.3</v>
       </c>
     </row>
-    <row r="28" ht="16" customHeight="1">
+    <row r="28" ht="18" customHeight="1">
       <c r="A28" s="3" t="n">
         <v>2024</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="29" ht="16" customHeight="1">
+    <row r="29" ht="18" customHeight="1">
       <c r="A29" s="3" t="n">
         <v>2025</v>
       </c>
@@ -1286,7 +1286,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1">
+    <row r="30" ht="18" customHeight="1">
       <c r="A30" s="3" t="n">
         <v>2024</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1">
+    <row r="31" ht="18" customHeight="1">
       <c r="A31" s="3" t="n">
         <v>2025</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="32" ht="16" customHeight="1">
+    <row r="32" ht="18" customHeight="1">
       <c r="A32" s="3" t="n">
         <v>2024</v>
       </c>
@@ -1367,7 +1367,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="33" ht="16" customHeight="1">
+    <row r="33" ht="18" customHeight="1">
       <c r="A33" s="3" t="n">
         <v>2025</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="34" ht="16" customHeight="1">
+    <row r="34" ht="18" customHeight="1">
       <c r="A34" s="3" t="n">
         <v>2024</v>
       </c>
@@ -1422,7 +1422,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="35" ht="16" customHeight="1">
+    <row r="35" ht="18" customHeight="1">
       <c r="A35" s="3" t="n">
         <v>2025</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>33.4</v>
       </c>
     </row>
-    <row r="36" ht="16" customHeight="1">
+    <row r="36" ht="18" customHeight="1">
       <c r="A36" s="3" t="n">
         <v>2024</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="37" ht="16" customHeight="1">
+    <row r="37" ht="18" customHeight="1">
       <c r="A37" s="3" t="n">
         <v>2025</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1">
+    <row r="38" ht="18" customHeight="1">
       <c r="A38" s="3" t="n">
         <v>2024</v>
       </c>
@@ -1544,7 +1544,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="39" ht="16" customHeight="1">
+    <row r="39" ht="18" customHeight="1">
       <c r="A39" s="3" t="n">
         <v>2025</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>34.4</v>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1">
+    <row r="40" ht="18" customHeight="1">
       <c r="A40" s="3" t="n">
         <v>2024</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>16.9</v>
       </c>
     </row>
-    <row r="41" ht="16" customHeight="1">
+    <row r="41" ht="18" customHeight="1">
       <c r="A41" s="3" t="n">
         <v>2025</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>35.6</v>
       </c>
     </row>
-    <row r="42" ht="16" customHeight="1">
+    <row r="42" ht="18" customHeight="1">
       <c r="A42" s="3" t="n">
         <v>2024</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="43" ht="16" customHeight="1">
+    <row r="43" ht="18" customHeight="1">
       <c r="A43" s="3" t="n">
         <v>2025</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>37.3</v>
       </c>
     </row>
-    <row r="44" ht="16" customHeight="1">
+    <row r="44" ht="18" customHeight="1">
       <c r="A44" s="3" t="n">
         <v>2024</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="45" ht="16" customHeight="1">
+    <row r="45" ht="18" customHeight="1">
       <c r="A45" s="3" t="n">
         <v>2025</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="46" ht="16" customHeight="1">
+    <row r="46" ht="18" customHeight="1">
       <c r="A46" s="3" t="n">
         <v>2024</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="47" ht="16" customHeight="1">
+    <row r="47" ht="18" customHeight="1">
       <c r="A47" s="3" t="n">
         <v>2025</v>
       </c>
@@ -1811,7 +1811,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="48" ht="16" customHeight="1">
+    <row r="48" ht="18" customHeight="1">
       <c r="A48" s="3" t="n">
         <v>2024</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="49" ht="16" customHeight="1">
+    <row r="49" ht="18" customHeight="1">
       <c r="A49" s="3" t="n">
         <v>2025</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="50" ht="16" customHeight="1">
+    <row r="50" ht="18" customHeight="1">
       <c r="A50" s="3" t="n">
         <v>2024</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" ht="16" customHeight="1">
+    <row r="51" ht="18" customHeight="1">
       <c r="A51" s="3" t="n">
         <v>2025</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" ht="16" customHeight="1">
+    <row r="52" ht="18" customHeight="1">
       <c r="A52" s="3" t="n">
         <v>2024</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" ht="16" customHeight="1">
+    <row r="53" ht="18" customHeight="1">
       <c r="A53" s="3" t="n">
         <v>2025</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>32.1</v>
       </c>
     </row>
-    <row r="54" ht="16" customHeight="1">
+    <row r="54" ht="18" customHeight="1">
       <c r="A54" s="3" t="n">
         <v>2024</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="55" ht="16" customHeight="1">
+    <row r="55" ht="18" customHeight="1">
       <c r="A55" s="3" t="n">
         <v>2025</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="56" ht="16" customHeight="1">
+    <row r="56" ht="18" customHeight="1">
       <c r="A56" s="3" t="n">
         <v>2024</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="57" ht="16" customHeight="1">
+    <row r="57" ht="18" customHeight="1">
       <c r="A57" s="3" t="n">
         <v>2025</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" ht="16" customHeight="1">
+    <row r="58" ht="18" customHeight="1">
       <c r="A58" s="3" t="n">
         <v>2024</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="59" ht="16" customHeight="1">
+    <row r="59" ht="18" customHeight="1">
       <c r="A59" s="3" t="n">
         <v>2025</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="60" ht="16" customHeight="1">
+    <row r="60" ht="18" customHeight="1">
       <c r="A60" s="3" t="n">
         <v>2024</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="61" ht="16" customHeight="1">
+    <row r="61" ht="18" customHeight="1">
       <c r="A61" s="3" t="n">
         <v>2025</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="62" ht="16" customHeight="1">
+    <row r="62" ht="18" customHeight="1">
       <c r="A62" s="3" t="n">
         <v>2024</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="63" ht="16" customHeight="1">
+    <row r="63" ht="18" customHeight="1">
       <c r="A63" s="3" t="n">
         <v>2025</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="64" ht="16" customHeight="1">
+    <row r="64" ht="18" customHeight="1">
       <c r="A64" s="3" t="n">
         <v>2024</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="65" ht="16" customHeight="1">
+    <row r="65" ht="18" customHeight="1">
       <c r="A65" s="3" t="n">
         <v>2025</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="66" ht="16" customHeight="1">
+    <row r="66" ht="18" customHeight="1">
       <c r="A66" s="3" t="n">
         <v>2024</v>
       </c>
@@ -2347,7 +2347,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="67" ht="16" customHeight="1">
+    <row r="67" ht="18" customHeight="1">
       <c r="A67" s="3" t="n">
         <v>2025</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>36.6</v>
       </c>
     </row>
-    <row r="68" ht="16" customHeight="1">
+    <row r="68" ht="18" customHeight="1">
       <c r="A68" s="3" t="n">
         <v>2024</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="69" ht="16" customHeight="1">
+    <row r="69" ht="18" customHeight="1">
       <c r="A69" s="3" t="n">
         <v>2025</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>35.9</v>
       </c>
     </row>
-    <row r="70" ht="16" customHeight="1">
+    <row r="70" ht="18" customHeight="1">
       <c r="A70" s="3" t="n">
         <v>2024</v>
       </c>
@@ -2466,7 +2466,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" ht="16" customHeight="1">
+    <row r="71" ht="18" customHeight="1">
       <c r="A71" s="3" t="n">
         <v>2025</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>36.2</v>
       </c>
     </row>
-    <row r="72" ht="16" customHeight="1">
+    <row r="72" ht="18" customHeight="1">
       <c r="A72" s="3" t="n">
         <v>2024</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="73" ht="16" customHeight="1">
+    <row r="73" ht="18" customHeight="1">
       <c r="A73" s="3" t="n">
         <v>2025</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="74" ht="16" customHeight="1">
+    <row r="74" ht="18" customHeight="1">
       <c r="A74" s="3" t="n">
         <v>2024</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="75" ht="16" customHeight="1">
+    <row r="75" ht="18" customHeight="1">
       <c r="A75" s="3" t="n">
         <v>2025</v>
       </c>
@@ -2614,7 +2614,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="76" ht="16" customHeight="1">
+    <row r="76" ht="18" customHeight="1">
       <c r="A76" s="3" t="n">
         <v>2024</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>9.800000000000001</v>
       </c>
     </row>
-    <row r="77" ht="16" customHeight="1">
+    <row r="77" ht="18" customHeight="1">
       <c r="A77" s="3" t="n">
         <v>2025</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="78" ht="16" customHeight="1">
+    <row r="78" ht="18" customHeight="1">
       <c r="A78" s="3" t="n">
         <v>2024</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="79" ht="16" customHeight="1">
+    <row r="79" ht="18" customHeight="1">
       <c r="A79" s="3" t="n">
         <v>2025</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="80" ht="16" customHeight="1">
+    <row r="80" ht="18" customHeight="1">
       <c r="A80" s="3" t="n">
         <v>2024</v>
       </c>
@@ -2774,7 +2774,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="81" ht="16" customHeight="1">
+    <row r="81" ht="18" customHeight="1">
       <c r="A81" s="3" t="n">
         <v>2025</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>30.4</v>
       </c>
     </row>
-    <row r="82" ht="16" customHeight="1">
+    <row r="82" ht="18" customHeight="1">
       <c r="A82" s="3" t="n">
         <v>2024</v>
       </c>
@@ -2835,7 +2835,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="83" ht="16" customHeight="1">
+    <row r="83" ht="18" customHeight="1">
       <c r="A83" s="3" t="n">
         <v>2025</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>29.3</v>
       </c>
     </row>
-    <row r="84" ht="16" customHeight="1">
+    <row r="84" ht="18" customHeight="1">
       <c r="A84" s="3" t="n">
         <v>2024</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="85" ht="16" customHeight="1">
+    <row r="85" ht="18" customHeight="1">
       <c r="A85" s="3" t="n">
         <v>2025</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="86" ht="16" customHeight="1">
+    <row r="86" ht="18" customHeight="1">
       <c r="A86" s="3" t="n">
         <v>2024</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="87" ht="16" customHeight="1">
+    <row r="87" ht="18" customHeight="1">
       <c r="A87" s="3" t="n">
         <v>2025</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="88" ht="16" customHeight="1">
+    <row r="88" ht="18" customHeight="1">
       <c r="A88" s="3" t="n">
         <v>2024</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="89" ht="16" customHeight="1">
+    <row r="89" ht="18" customHeight="1">
       <c r="A89" s="3" t="n">
         <v>2025</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="90" ht="16" customHeight="1">
+    <row r="90" ht="18" customHeight="1">
       <c r="A90" s="3" t="n">
         <v>2024</v>
       </c>
@@ -3076,7 +3076,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="91" ht="16" customHeight="1">
+    <row r="91" ht="18" customHeight="1">
       <c r="A91" s="3" t="n">
         <v>2025</v>
       </c>
@@ -3105,7 +3105,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="92" ht="16" customHeight="1">
+    <row r="92" ht="18" customHeight="1">
       <c r="A92" s="3" t="n">
         <v>2024</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="93" ht="16" customHeight="1">
+    <row r="93" ht="18" customHeight="1">
       <c r="A93" s="3" t="n">
         <v>2025</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="94" ht="16" customHeight="1">
+    <row r="94" ht="18" customHeight="1">
       <c r="A94" s="3" t="n">
         <v>2024</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="95" ht="16" customHeight="1">
+    <row r="95" ht="18" customHeight="1">
       <c r="A95" s="3" t="n">
         <v>2025</v>
       </c>
@@ -3227,7 +3227,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="96" ht="16" customHeight="1">
+    <row r="96" ht="18" customHeight="1">
       <c r="A96" s="3" t="n">
         <v>2024</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="97" ht="16" customHeight="1">
+    <row r="97" ht="18" customHeight="1">
       <c r="A97" s="3" t="n">
         <v>2025</v>
       </c>
@@ -3279,7 +3279,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="98" ht="16" customHeight="1">
+    <row r="98" ht="18" customHeight="1">
       <c r="A98" s="3" t="n">
         <v>2024</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="99" ht="16" customHeight="1">
+    <row r="99" ht="18" customHeight="1">
       <c r="A99" s="3" t="n">
         <v>2025</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>37.3</v>
       </c>
     </row>
-    <row r="100" ht="16" customHeight="1">
+    <row r="100" ht="18" customHeight="1">
       <c r="A100" s="3" t="n">
         <v>2024</v>
       </c>
@@ -3354,7 +3354,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="101" ht="16" customHeight="1">
+    <row r="101" ht="18" customHeight="1">
       <c r="A101" s="3" t="n">
         <v>2025</v>
       </c>
@@ -3386,7 +3386,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="102" ht="16" customHeight="1">
+    <row r="102" ht="18" customHeight="1">
       <c r="A102" s="3" t="n">
         <v>2024</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="103" ht="16" customHeight="1">
+    <row r="103" ht="18" customHeight="1">
       <c r="A103" s="3" t="n">
         <v>2025</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="104" ht="16" customHeight="1">
+    <row r="104" ht="18" customHeight="1">
       <c r="A104" s="3" t="n">
         <v>2024</v>
       </c>
@@ -3464,7 +3464,7 @@
         <v>48.7</v>
       </c>
     </row>
-    <row r="105" ht="16" customHeight="1">
+    <row r="105" ht="18" customHeight="1">
       <c r="A105" s="3" t="n">
         <v>2025</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="106" ht="16" customHeight="1">
+    <row r="106" ht="18" customHeight="1">
       <c r="A106" s="3" t="n">
         <v>2024</v>
       </c>
@@ -3507,7 +3507,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="107" ht="16" customHeight="1">
+    <row r="107" ht="18" customHeight="1">
       <c r="A107" s="3" t="n">
         <v>2025</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>146.2</v>
       </c>
     </row>
-    <row r="108" ht="16" customHeight="1">
+    <row r="108" ht="18" customHeight="1">
       <c r="A108" s="3" t="n">
         <v>2024</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>34.9</v>
       </c>
     </row>
-    <row r="109" ht="16" customHeight="1">
+    <row r="109" ht="18" customHeight="1">
       <c r="A109" s="3" t="n">
         <v>2025</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>31.3</v>
       </c>
     </row>
-    <row r="110" ht="16" customHeight="1">
+    <row r="110" ht="18" customHeight="1">
       <c r="A110" s="3" t="n">
         <v>2024</v>
       </c>
@@ -3614,7 +3614,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="111" ht="16" customHeight="1">
+    <row r="111" ht="18" customHeight="1">
       <c r="A111" s="3" t="n">
         <v>2025</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>38.4</v>
       </c>
     </row>
-    <row r="112" ht="16" customHeight="1">
+    <row r="112" ht="18" customHeight="1">
       <c r="A112" s="3" t="n">
         <v>2024</v>
       </c>
@@ -3678,7 +3678,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="113" ht="16" customHeight="1">
+    <row r="113" ht="18" customHeight="1">
       <c r="A113" s="3" t="n">
         <v>2025</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="114" ht="16" customHeight="1">
+    <row r="114" ht="18" customHeight="1">
       <c r="A114" s="3" t="n">
         <v>2024</v>
       </c>
@@ -3742,7 +3742,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="115" ht="16" customHeight="1">
+    <row r="115" ht="18" customHeight="1">
       <c r="A115" s="3" t="n">
         <v>2025</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="116" ht="16" customHeight="1">
+    <row r="116" ht="18" customHeight="1">
       <c r="A116" s="3" t="n">
         <v>2024</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" ht="16" customHeight="1">
+    <row r="117" ht="18" customHeight="1">
       <c r="A117" s="3" t="n">
         <v>2025</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>40.2</v>
       </c>
     </row>
-    <row r="118" ht="16" customHeight="1">
+    <row r="118" ht="18" customHeight="1">
       <c r="A118" s="3" t="n">
         <v>2024</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="119" ht="16" customHeight="1">
+    <row r="119" ht="18" customHeight="1">
       <c r="A119" s="3" t="n">
         <v>2025</v>
       </c>
@@ -3893,7 +3893,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="120" ht="16" customHeight="1">
+    <row r="120" ht="18" customHeight="1">
       <c r="A120" s="3" t="n">
         <v>2024</v>
       </c>
@@ -3925,7 +3925,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="121" ht="16" customHeight="1">
+    <row r="121" ht="18" customHeight="1">
       <c r="A121" s="3" t="n">
         <v>2025</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="122" ht="16" customHeight="1">
+    <row r="122" ht="18" customHeight="1">
       <c r="A122" s="3" t="n">
         <v>2024</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="123" ht="16" customHeight="1">
+    <row r="123" ht="18" customHeight="1">
       <c r="A123" s="3" t="n">
         <v>2025</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="124" ht="16" customHeight="1">
+    <row r="124" ht="18" customHeight="1">
       <c r="A124" s="3" t="n">
         <v>2024</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="125" ht="16" customHeight="1">
+    <row r="125" ht="18" customHeight="1">
       <c r="A125" s="3" t="n">
         <v>2025</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="126" ht="16" customHeight="1">
+    <row r="126" ht="18" customHeight="1">
       <c r="A126" s="3" t="n">
         <v>2024</v>
       </c>
@@ -4087,7 +4087,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="127" ht="16" customHeight="1">
+    <row r="127" ht="18" customHeight="1">
       <c r="A127" s="3" t="n">
         <v>2025</v>
       </c>
@@ -4116,7 +4116,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="128" ht="16" customHeight="1">
+    <row r="128" ht="18" customHeight="1">
       <c r="A128" s="3" t="n">
         <v>2024</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="129" ht="16" customHeight="1">
+    <row r="129" ht="18" customHeight="1">
       <c r="A129" s="3" t="n">
         <v>2025</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>28.3</v>
       </c>
     </row>
-    <row r="130" ht="16" customHeight="1">
+    <row r="130" ht="18" customHeight="1">
       <c r="A130" s="3" t="n">
         <v>2024</v>
       </c>
@@ -4197,7 +4197,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="131" ht="16" customHeight="1">
+    <row r="131" ht="18" customHeight="1">
       <c r="A131" s="3" t="n">
         <v>2025</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="132" ht="16" customHeight="1">
+    <row r="132" ht="18" customHeight="1">
       <c r="A132" s="3" t="n">
         <v>2024</v>
       </c>
@@ -4255,7 +4255,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="133" ht="16" customHeight="1">
+    <row r="133" ht="18" customHeight="1">
       <c r="A133" s="3" t="n">
         <v>2025</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>34.6</v>
       </c>
     </row>
-    <row r="134" ht="16" customHeight="1">
+    <row r="134" ht="18" customHeight="1">
       <c r="A134" s="3" t="n">
         <v>2024</v>
       </c>
@@ -4313,7 +4313,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="135" ht="16" customHeight="1">
+    <row r="135" ht="18" customHeight="1">
       <c r="A135" s="3" t="n">
         <v>2025</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>29.2</v>
       </c>
     </row>
-    <row r="136" ht="16" customHeight="1">
+    <row r="136" ht="18" customHeight="1">
       <c r="A136" s="3" t="n">
         <v>2024</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="137" ht="16" customHeight="1">
+    <row r="137" ht="18" customHeight="1">
       <c r="A137" s="3" t="n">
         <v>2025</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>34.1</v>
       </c>
     </row>
-    <row r="138" ht="16" customHeight="1">
+    <row r="138" ht="18" customHeight="1">
       <c r="A138" s="3" t="n">
         <v>2024</v>
       </c>
@@ -4429,7 +4429,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="139" ht="16" customHeight="1">
+    <row r="139" ht="18" customHeight="1">
       <c r="A139" s="3" t="n">
         <v>2025</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>34.4</v>
       </c>
     </row>
-    <row r="140" ht="16" customHeight="1">
+    <row r="140" ht="18" customHeight="1">
       <c r="A140" s="3" t="n">
         <v>2024</v>
       </c>
@@ -4487,7 +4487,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="141" ht="16" customHeight="1">
+    <row r="141" ht="18" customHeight="1">
       <c r="A141" s="3" t="n">
         <v>2025</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="142" ht="16" customHeight="1">
+    <row r="142" ht="18" customHeight="1">
       <c r="A142" s="3" t="n">
         <v>2024</v>
       </c>
@@ -4533,7 +4533,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="143" ht="16" customHeight="1">
+    <row r="143" ht="18" customHeight="1">
       <c r="A143" s="3" t="n">
         <v>2025</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="144" ht="16" customHeight="1">
+    <row r="144" ht="18" customHeight="1">
       <c r="A144" s="3" t="n">
         <v>2024</v>
       </c>
@@ -4579,7 +4579,7 @@
         <v>84.8</v>
       </c>
     </row>
-    <row r="145" ht="16" customHeight="1">
+    <row r="145" ht="18" customHeight="1">
       <c r="A145" s="3" t="n">
         <v>2025</v>
       </c>
@@ -4599,7 +4599,7 @@
         <v>73.5</v>
       </c>
     </row>
-    <row r="146" ht="16" customHeight="1">
+    <row r="146" ht="18" customHeight="1">
       <c r="A146" s="3" t="n">
         <v>2024</v>
       </c>
@@ -4622,7 +4622,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="147" ht="16" customHeight="1">
+    <row r="147" ht="18" customHeight="1">
       <c r="A147" s="3" t="n">
         <v>2025</v>
       </c>
@@ -4648,7 +4648,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="148" ht="16" customHeight="1">
+    <row r="148" ht="18" customHeight="1">
       <c r="A148" s="3" t="n">
         <v>2024</v>
       </c>
@@ -4674,7 +4674,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="149" ht="16" customHeight="1">
+    <row r="149" ht="18" customHeight="1">
       <c r="A149" s="3" t="n">
         <v>2025</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>2872</v>
       </c>
     </row>
-    <row r="150" ht="16" customHeight="1">
+    <row r="150" ht="18" customHeight="1">
       <c r="A150" s="3" t="n">
         <v>2024</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="151" ht="16" customHeight="1">
+    <row r="151" ht="18" customHeight="1">
       <c r="A151" s="3" t="n">
         <v>2025</v>
       </c>
@@ -4767,7 +4767,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="152" ht="16" customHeight="1">
+    <row r="152" ht="18" customHeight="1">
       <c r="A152" s="3" t="n">
         <v>2024</v>
       </c>
@@ -4799,7 +4799,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="153" ht="16" customHeight="1">
+    <row r="153" ht="18" customHeight="1">
       <c r="A153" s="3" t="n">
         <v>2025</v>
       </c>
@@ -4831,7 +4831,7 @@
         <v>38.9</v>
       </c>
     </row>
-    <row r="154" ht="16" customHeight="1">
+    <row r="154" ht="18" customHeight="1">
       <c r="A154" s="3" t="n">
         <v>2024</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="155" ht="16" customHeight="1">
+    <row r="155" ht="18" customHeight="1">
       <c r="A155" s="3" t="n">
         <v>2025</v>
       </c>
@@ -4895,7 +4895,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="156" ht="16" customHeight="1">
+    <row r="156" ht="18" customHeight="1">
       <c r="A156" s="3" t="n">
         <v>2024</v>
       </c>
@@ -4927,7 +4927,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="157" ht="16" customHeight="1">
+    <row r="157" ht="18" customHeight="1">
       <c r="A157" s="3" t="n">
         <v>2025</v>
       </c>
@@ -4959,7 +4959,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="158" ht="16" customHeight="1">
+    <row r="158" ht="18" customHeight="1">
       <c r="A158" s="3" t="n">
         <v>2024</v>
       </c>
@@ -4988,7 +4988,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="159" ht="16" customHeight="1">
+    <row r="159" ht="18" customHeight="1">
       <c r="A159" s="3" t="n">
         <v>2025</v>
       </c>
@@ -5017,7 +5017,7 @@
         <v>42.2</v>
       </c>
     </row>
-    <row r="160" ht="16" customHeight="1">
+    <row r="160" ht="18" customHeight="1">
       <c r="A160" s="3" t="n">
         <v>2024</v>
       </c>
@@ -5040,7 +5040,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="161" ht="16" customHeight="1">
+    <row r="161" ht="18" customHeight="1">
       <c r="A161" s="3" t="n">
         <v>2025</v>
       </c>
@@ -5066,7 +5066,7 @@
         <v>37.3</v>
       </c>
     </row>
-    <row r="162" ht="16" customHeight="1">
+    <row r="162" ht="18" customHeight="1">
       <c r="A162" s="3" t="n">
         <v>2024</v>
       </c>
@@ -5095,7 +5095,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="163" ht="16" customHeight="1">
+    <row r="163" ht="18" customHeight="1">
       <c r="A163" s="3" t="n">
         <v>2025</v>
       </c>
@@ -5124,7 +5124,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="164" ht="16" customHeight="1">
+    <row r="164" ht="18" customHeight="1">
       <c r="A164" s="3" t="n">
         <v>2024</v>
       </c>
@@ -5156,7 +5156,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="165" ht="16" customHeight="1">
+    <row r="165" ht="18" customHeight="1">
       <c r="A165" s="3" t="n">
         <v>2025</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="166" ht="16" customHeight="1">
+    <row r="166" ht="18" customHeight="1">
       <c r="A166" s="3" t="n">
         <v>2024</v>
       </c>
@@ -5214,7 +5214,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="167" ht="16" customHeight="1">
+    <row r="167" ht="18" customHeight="1">
       <c r="A167" s="3" t="n">
         <v>2025</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="168" ht="16" customHeight="1">
+    <row r="168" ht="18" customHeight="1">
       <c r="A168" s="3" t="n">
         <v>2024</v>
       </c>
@@ -5269,7 +5269,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="169" ht="16" customHeight="1">
+    <row r="169" ht="18" customHeight="1">
       <c r="A169" s="3" t="n">
         <v>2025</v>
       </c>
@@ -5298,7 +5298,7 @@
         <v>28.7</v>
       </c>
     </row>
-    <row r="170" ht="16" customHeight="1">
+    <row r="170" ht="18" customHeight="1">
       <c r="A170" s="3" t="n">
         <v>2024</v>
       </c>
@@ -5327,7 +5327,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="171" ht="16" customHeight="1">
+    <row r="171" ht="18" customHeight="1">
       <c r="A171" s="3" t="n">
         <v>2025</v>
       </c>
@@ -5350,7 +5350,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="172" ht="16" customHeight="1">
+    <row r="172" ht="18" customHeight="1">
       <c r="A172" s="3" t="n">
         <v>2024</v>
       </c>
@@ -5376,7 +5376,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="173" ht="16" customHeight="1">
+    <row r="173" ht="18" customHeight="1">
       <c r="A173" s="3" t="n">
         <v>2025</v>
       </c>
@@ -5405,7 +5405,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="174" ht="16" customHeight="1">
+    <row r="174" ht="18" customHeight="1">
       <c r="A174" s="3" t="n">
         <v>2024</v>
       </c>
@@ -5431,7 +5431,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="175" ht="16" customHeight="1">
+    <row r="175" ht="18" customHeight="1">
       <c r="A175" s="3" t="n">
         <v>2025</v>
       </c>
@@ -5457,7 +5457,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="176" ht="16" customHeight="1">
+    <row r="176" ht="18" customHeight="1">
       <c r="A176" s="3" t="n">
         <v>2024</v>
       </c>
@@ -5486,7 +5486,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="177" ht="16" customHeight="1">
+    <row r="177" ht="18" customHeight="1">
       <c r="A177" s="3" t="n">
         <v>2025</v>
       </c>
@@ -5515,7 +5515,7 @@
         <v>39.7</v>
       </c>
     </row>
-    <row r="178" ht="16" customHeight="1">
+    <row r="178" ht="18" customHeight="1">
       <c r="A178" s="3" t="n">
         <v>2024</v>
       </c>
@@ -5547,7 +5547,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="179" ht="16" customHeight="1">
+    <row r="179" ht="18" customHeight="1">
       <c r="A179" s="3" t="n">
         <v>2025</v>
       </c>
@@ -5576,7 +5576,7 @@
         <v>1718</v>
       </c>
     </row>
-    <row r="180" ht="16" customHeight="1">
+    <row r="180" ht="18" customHeight="1">
       <c r="A180" s="3" t="n">
         <v>2024</v>
       </c>
@@ -5602,7 +5602,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="181" ht="16" customHeight="1">
+    <row r="181" ht="18" customHeight="1">
       <c r="A181" s="3" t="n">
         <v>2025</v>
       </c>
@@ -5631,7 +5631,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="182" ht="16" customHeight="1">
+    <row r="182" ht="18" customHeight="1">
       <c r="A182" s="3" t="n">
         <v>2024</v>
       </c>
@@ -5657,7 +5657,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="183" ht="16" customHeight="1">
+    <row r="183" ht="18" customHeight="1">
       <c r="A183" s="3" t="n">
         <v>2025</v>
       </c>
@@ -5680,7 +5680,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="184" ht="16" customHeight="1">
+    <row r="184" ht="18" customHeight="1">
       <c r="A184" s="3" t="n">
         <v>2024</v>
       </c>
@@ -5706,7 +5706,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="185" ht="16" customHeight="1">
+    <row r="185" ht="18" customHeight="1">
       <c r="A185" s="3" t="n">
         <v>2025</v>
       </c>
@@ -5735,7 +5735,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="186" ht="16" customHeight="1">
+    <row r="186" ht="18" customHeight="1">
       <c r="A186" s="3" t="n">
         <v>2024</v>
       </c>
@@ -5761,7 +5761,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="187" ht="16" customHeight="1">
+    <row r="187" ht="18" customHeight="1">
       <c r="A187" s="3" t="n">
         <v>2025</v>
       </c>
@@ -5790,7 +5790,7 @@
         <v>36.6</v>
       </c>
     </row>
-    <row r="188" ht="16" customHeight="1">
+    <row r="188" ht="18" customHeight="1">
       <c r="A188" s="3" t="n">
         <v>2024</v>
       </c>
@@ -5810,7 +5810,7 @@
         <v>62.2</v>
       </c>
     </row>
-    <row r="189" ht="16" customHeight="1">
+    <row r="189" ht="18" customHeight="1">
       <c r="A189" s="3" t="n">
         <v>2025</v>
       </c>
@@ -5830,7 +5830,7 @@
         <v>77.8</v>
       </c>
     </row>
-    <row r="190" ht="16" customHeight="1">
+    <row r="190" ht="18" customHeight="1">
       <c r="A190" s="3" t="n">
         <v>2024</v>
       </c>
@@ -5853,7 +5853,7 @@
         <v>58.1</v>
       </c>
     </row>
-    <row r="191" ht="16" customHeight="1">
+    <row r="191" ht="18" customHeight="1">
       <c r="A191" s="3" t="n">
         <v>2025</v>
       </c>
@@ -5879,7 +5879,7 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="192" ht="16" customHeight="1">
+    <row r="192" ht="18" customHeight="1">
       <c r="A192" s="3" t="n">
         <v>2024</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="193" ht="16" customHeight="1">
+    <row r="193" ht="18" customHeight="1">
       <c r="A193" s="3" t="n">
         <v>2025</v>
       </c>
@@ -5940,7 +5940,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="194" ht="16" customHeight="1">
+    <row r="194" ht="18" customHeight="1">
       <c r="A194" s="3" t="n">
         <v>2024</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="195" ht="16" customHeight="1">
+    <row r="195" ht="18" customHeight="1">
       <c r="A195" s="3" t="n">
         <v>2025</v>
       </c>
@@ -6004,7 +6004,7 @@
         <v>31.6</v>
       </c>
     </row>
-    <row r="196" ht="16" customHeight="1">
+    <row r="196" ht="18" customHeight="1">
       <c r="A196" s="3" t="n">
         <v>2024</v>
       </c>
@@ -6036,7 +6036,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="197" ht="16" customHeight="1">
+    <row r="197" ht="18" customHeight="1">
       <c r="A197" s="3" t="n">
         <v>2025</v>
       </c>
@@ -6068,7 +6068,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="198" ht="16" customHeight="1">
+    <row r="198" ht="18" customHeight="1">
       <c r="A198" s="3" t="n">
         <v>2024</v>
       </c>
@@ -6100,7 +6100,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="199" ht="16" customHeight="1">
+    <row r="199" ht="18" customHeight="1">
       <c r="A199" s="3" t="n">
         <v>2025</v>
       </c>
@@ -6132,7 +6132,7 @@
         <v>32.2</v>
       </c>
     </row>
-    <row r="200" ht="16" customHeight="1">
+    <row r="200" ht="18" customHeight="1">
       <c r="A200" s="3" t="n">
         <v>2024</v>
       </c>
@@ -6161,7 +6161,7 @@
         <v>18.4</v>
       </c>
     </row>
-    <row r="201" ht="16" customHeight="1">
+    <row r="201" ht="18" customHeight="1">
       <c r="A201" s="3" t="n">
         <v>2025</v>
       </c>
@@ -6190,7 +6190,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="202" ht="16" customHeight="1">
+    <row r="202" ht="18" customHeight="1">
       <c r="A202" s="3" t="n">
         <v>2024</v>
       </c>
@@ -6219,7 +6219,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="203" ht="16" customHeight="1">
+    <row r="203" ht="18" customHeight="1">
       <c r="A203" s="3" t="n">
         <v>2025</v>
       </c>
@@ -6248,7 +6248,7 @@
         <v>33.2</v>
       </c>
     </row>
-    <row r="204" ht="16" customHeight="1">
+    <row r="204" ht="18" customHeight="1">
       <c r="A204" s="3" t="n">
         <v>2024</v>
       </c>
@@ -6277,7 +6277,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="205" ht="16" customHeight="1">
+    <row r="205" ht="18" customHeight="1">
       <c r="A205" s="3" t="n">
         <v>2025</v>
       </c>
@@ -6306,7 +6306,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="206" ht="16" customHeight="1">
+    <row r="206" ht="18" customHeight="1">
       <c r="A206" s="3" t="n">
         <v>2024</v>
       </c>
@@ -6335,7 +6335,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="207" ht="16" customHeight="1">
+    <row r="207" ht="18" customHeight="1">
       <c r="A207" s="3" t="n">
         <v>2025</v>
       </c>
@@ -6364,7 +6364,7 @@
         <v>28.7</v>
       </c>
     </row>
-    <row r="208" ht="16" customHeight="1">
+    <row r="208" ht="18" customHeight="1">
       <c r="A208" s="3" t="n">
         <v>2024</v>
       </c>
@@ -6393,7 +6393,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="209" ht="16" customHeight="1">
+    <row r="209" ht="18" customHeight="1">
       <c r="A209" s="3" t="n">
         <v>2025</v>
       </c>
@@ -6422,7 +6422,7 @@
         <v>38.3</v>
       </c>
     </row>
-    <row r="210" ht="16" customHeight="1">
+    <row r="210" ht="18" customHeight="1">
       <c r="A210" s="3" t="n">
         <v>2024</v>
       </c>
@@ -6451,7 +6451,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="211" ht="16" customHeight="1">
+    <row r="211" ht="18" customHeight="1">
       <c r="A211" s="3" t="n">
         <v>2025</v>
       </c>
@@ -6480,7 +6480,7 @@
         <v>33.7</v>
       </c>
     </row>
-    <row r="212" ht="16" customHeight="1">
+    <row r="212" ht="18" customHeight="1">
       <c r="A212" s="3" t="n">
         <v>2024</v>
       </c>
@@ -6506,7 +6506,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="213" ht="16" customHeight="1">
+    <row r="213" ht="18" customHeight="1">
       <c r="A213" s="3" t="n">
         <v>2025</v>
       </c>
@@ -6535,7 +6535,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="214" ht="16" customHeight="1">
+    <row r="214" ht="18" customHeight="1">
       <c r="A214" s="3" t="n">
         <v>2024</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="215" ht="16" customHeight="1">
+    <row r="215" ht="18" customHeight="1">
       <c r="A215" s="3" t="n">
         <v>2025</v>
       </c>
@@ -6590,7 +6590,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="216" ht="16" customHeight="1">
+    <row r="216" ht="18" customHeight="1">
       <c r="A216" s="3" t="n">
         <v>2024</v>
       </c>
@@ -6616,7 +6616,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="217" ht="16" customHeight="1">
+    <row r="217" ht="18" customHeight="1">
       <c r="A217" s="3" t="n">
         <v>2025</v>
       </c>
@@ -6645,7 +6645,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="218" ht="16" customHeight="1">
+    <row r="218" ht="18" customHeight="1">
       <c r="A218" s="3" t="n">
         <v>2024</v>
       </c>
@@ -6677,7 +6677,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="219" ht="16" customHeight="1">
+    <row r="219" ht="18" customHeight="1">
       <c r="A219" s="3" t="n">
         <v>2025</v>
       </c>
@@ -6706,7 +6706,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="220" ht="16" customHeight="1">
+    <row r="220" ht="18" customHeight="1">
       <c r="A220" s="3" t="n">
         <v>2024</v>
       </c>
@@ -6735,7 +6735,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="221" ht="16" customHeight="1">
+    <row r="221" ht="18" customHeight="1">
       <c r="A221" s="3" t="n">
         <v>2025</v>
       </c>
@@ -6764,7 +6764,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="222" ht="16" customHeight="1">
+    <row r="222" ht="18" customHeight="1">
       <c r="A222" s="3" t="n">
         <v>2024</v>
       </c>
@@ -6793,7 +6793,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="223" ht="16" customHeight="1">
+    <row r="223" ht="18" customHeight="1">
       <c r="A223" s="3" t="n">
         <v>2025</v>
       </c>
@@ -6819,7 +6819,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="224" ht="16" customHeight="1">
+    <row r="224" ht="18" customHeight="1">
       <c r="A224" s="3" t="n">
         <v>2024</v>
       </c>
@@ -6848,7 +6848,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="225" ht="16" customHeight="1">
+    <row r="225" ht="18" customHeight="1">
       <c r="A225" s="3" t="n">
         <v>2025</v>
       </c>
@@ -6874,7 +6874,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="226" ht="16" customHeight="1">
+    <row r="226" ht="18" customHeight="1">
       <c r="A226" s="3" t="n">
         <v>2024</v>
       </c>
@@ -6897,7 +6897,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="227" ht="16" customHeight="1">
+    <row r="227" ht="18" customHeight="1">
       <c r="A227" s="3" t="n">
         <v>2025</v>
       </c>
@@ -6920,7 +6920,7 @@
         <v>47.2</v>
       </c>
     </row>
-    <row r="228" ht="16" customHeight="1">
+    <row r="228" ht="18" customHeight="1">
       <c r="A228" s="3" t="n">
         <v>2024</v>
       </c>
@@ -6949,7 +6949,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="229" ht="16" customHeight="1">
+    <row r="229" ht="18" customHeight="1">
       <c r="A229" s="3" t="n">
         <v>2025</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>32.3</v>
       </c>
     </row>
-    <row r="230" ht="16" customHeight="1">
+    <row r="230" ht="18" customHeight="1">
       <c r="A230" s="3" t="n">
         <v>2024</v>
       </c>
@@ -7010,7 +7010,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" ht="16" customHeight="1">
+    <row r="231" ht="18" customHeight="1">
       <c r="A231" s="3" t="n">
         <v>2025</v>
       </c>
@@ -7039,7 +7039,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="232" ht="16" customHeight="1">
+    <row r="232" ht="18" customHeight="1">
       <c r="A232" s="3" t="n">
         <v>2024</v>
       </c>
@@ -7065,7 +7065,7 @@
         <v>1768</v>
       </c>
     </row>
-    <row r="233" ht="16" customHeight="1">
+    <row r="233" ht="18" customHeight="1">
       <c r="A233" s="3" t="n">
         <v>2025</v>
       </c>
@@ -7097,7 +7097,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="234" ht="16" customHeight="1">
+    <row r="234" ht="18" customHeight="1">
       <c r="A234" s="3" t="n">
         <v>2024</v>
       </c>
@@ -7129,7 +7129,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="235" ht="16" customHeight="1">
+    <row r="235" ht="18" customHeight="1">
       <c r="A235" s="3" t="n">
         <v>2025</v>
       </c>
@@ -7161,7 +7161,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="236" ht="16" customHeight="1">
+    <row r="236" ht="18" customHeight="1">
       <c r="A236" s="3" t="n">
         <v>2024</v>
       </c>
@@ -7187,7 +7187,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="237" ht="16" customHeight="1">
+    <row r="237" ht="18" customHeight="1">
       <c r="A237" s="3" t="n">
         <v>2025</v>
       </c>
@@ -7216,7 +7216,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="238" ht="16" customHeight="1">
+    <row r="238" ht="18" customHeight="1">
       <c r="A238" s="3" t="n">
         <v>2024</v>
       </c>
@@ -7245,7 +7245,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="239" ht="16" customHeight="1">
+    <row r="239" ht="18" customHeight="1">
       <c r="A239" s="3" t="n">
         <v>2025</v>
       </c>
@@ -7274,7 +7274,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="240" ht="16" customHeight="1">
+    <row r="240" ht="18" customHeight="1">
       <c r="A240" s="3" t="n">
         <v>2024</v>
       </c>
@@ -7306,7 +7306,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="241" ht="16" customHeight="1">
+    <row r="241" ht="18" customHeight="1">
       <c r="A241" s="3" t="n">
         <v>2025</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="242" ht="16" customHeight="1">
+    <row r="242" ht="18" customHeight="1">
       <c r="A242" s="3" t="n">
         <v>2024</v>
       </c>
@@ -7367,7 +7367,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="243" ht="16" customHeight="1">
+    <row r="243" ht="18" customHeight="1">
       <c r="A243" s="3" t="n">
         <v>2025</v>
       </c>
@@ -7390,7 +7390,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="244" ht="16" customHeight="1">
+    <row r="244" ht="18" customHeight="1">
       <c r="A244" s="3" t="n">
         <v>2024</v>
       </c>
@@ -7419,7 +7419,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="245" ht="16" customHeight="1">
+    <row r="245" ht="18" customHeight="1">
       <c r="A245" s="3" t="n">
         <v>2025</v>
       </c>
@@ -7451,7 +7451,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="246" ht="16" customHeight="1">
+    <row r="246" ht="18" customHeight="1">
       <c r="A246" s="3" t="n">
         <v>2024</v>
       </c>
@@ -7483,7 +7483,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="247" ht="16" customHeight="1">
+    <row r="247" ht="18" customHeight="1">
       <c r="A247" s="3" t="n">
         <v>2025</v>
       </c>
@@ -7509,7 +7509,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="248" ht="16" customHeight="1">
+    <row r="248" ht="18" customHeight="1">
       <c r="A248" s="3" t="n">
         <v>2024</v>
       </c>
@@ -7541,7 +7541,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="249" ht="16" customHeight="1">
+    <row r="249" ht="18" customHeight="1">
       <c r="A249" s="3" t="n">
         <v>2025</v>
       </c>
@@ -7567,7 +7567,7 @@
         <v>38.8</v>
       </c>
     </row>
-    <row r="250" ht="16" customHeight="1">
+    <row r="250" ht="18" customHeight="1">
       <c r="A250" s="3" t="n">
         <v>2024</v>
       </c>
@@ -7593,7 +7593,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="251" ht="16" customHeight="1">
+    <row r="251" ht="18" customHeight="1">
       <c r="A251" s="3" t="n">
         <v>2025</v>
       </c>
@@ -7625,7 +7625,7 @@
         <v>41.3</v>
       </c>
     </row>
-    <row r="252" ht="16" customHeight="1">
+    <row r="252" ht="18" customHeight="1">
       <c r="A252" s="3" t="n">
         <v>2024</v>
       </c>
@@ -7648,7 +7648,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="253" ht="16" customHeight="1">
+    <row r="253" ht="18" customHeight="1">
       <c r="A253" s="3" t="n">
         <v>2025</v>
       </c>
@@ -7677,7 +7677,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="254" ht="16" customHeight="1">
+    <row r="254" ht="18" customHeight="1">
       <c r="A254" s="3" t="n">
         <v>2024</v>
       </c>
@@ -7709,7 +7709,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="255" ht="16" customHeight="1">
+    <row r="255" ht="18" customHeight="1">
       <c r="A255" s="3" t="n">
         <v>2025</v>
       </c>
@@ -7735,7 +7735,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="256" ht="16" customHeight="1">
+    <row r="256" ht="18" customHeight="1">
       <c r="A256" s="3" t="n">
         <v>2024</v>
       </c>
@@ -7764,7 +7764,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="257" ht="16" customHeight="1">
+    <row r="257" ht="18" customHeight="1">
       <c r="A257" s="3" t="n">
         <v>2025</v>
       </c>
@@ -7793,7 +7793,7 @@
         <v>31.9</v>
       </c>
     </row>
-    <row r="258" ht="16" customHeight="1">
+    <row r="258" ht="18" customHeight="1">
       <c r="A258" s="3" t="n">
         <v>2024</v>
       </c>
@@ -7822,7 +7822,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="259" ht="16" customHeight="1">
+    <row r="259" ht="18" customHeight="1">
       <c r="A259" s="3" t="n">
         <v>2025</v>
       </c>
@@ -7851,7 +7851,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="260" ht="16" customHeight="1">
+    <row r="260" ht="18" customHeight="1">
       <c r="A260" s="3" t="n">
         <v>2024</v>
       </c>
@@ -7883,7 +7883,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="261" ht="16" customHeight="1">
+    <row r="261" ht="18" customHeight="1">
       <c r="A261" s="3" t="n">
         <v>2025</v>
       </c>
@@ -7912,7 +7912,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="262" ht="16" customHeight="1">
+    <row r="262" ht="18" customHeight="1">
       <c r="A262" s="3" t="n">
         <v>2024</v>
       </c>
@@ -7944,7 +7944,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="263" ht="16" customHeight="1">
+    <row r="263" ht="18" customHeight="1">
       <c r="A263" s="3" t="n">
         <v>2025</v>
       </c>
@@ -7976,7 +7976,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="264" ht="16" customHeight="1">
+    <row r="264" ht="18" customHeight="1">
       <c r="A264" s="3" t="n">
         <v>2024</v>
       </c>
@@ -8008,7 +8008,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="265" ht="16" customHeight="1">
+    <row r="265" ht="18" customHeight="1">
       <c r="A265" s="3" t="n">
         <v>2025</v>
       </c>
@@ -8040,7 +8040,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="266" ht="16" customHeight="1">
+    <row r="266" ht="18" customHeight="1">
       <c r="A266" s="3" t="n">
         <v>2024</v>
       </c>
@@ -8072,7 +8072,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="267" ht="16" customHeight="1">
+    <row r="267" ht="18" customHeight="1">
       <c r="A267" s="3" t="n">
         <v>2025</v>
       </c>
@@ -8104,7 +8104,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="268" ht="16" customHeight="1">
+    <row r="268" ht="18" customHeight="1">
       <c r="A268" s="3" t="n">
         <v>2024</v>
       </c>
@@ -8133,7 +8133,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="269" ht="16" customHeight="1">
+    <row r="269" ht="18" customHeight="1">
       <c r="A269" s="3" t="n">
         <v>2025</v>
       </c>
@@ -8165,7 +8165,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="270" ht="16" customHeight="1">
+    <row r="270" ht="18" customHeight="1">
       <c r="A270" s="3" t="n">
         <v>2024</v>
       </c>
@@ -8197,7 +8197,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="271" ht="16" customHeight="1">
+    <row r="271" ht="18" customHeight="1">
       <c r="A271" s="3" t="n">
         <v>2025</v>
       </c>
@@ -8226,7 +8226,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="272" ht="16" customHeight="1">
+    <row r="272" ht="18" customHeight="1">
       <c r="A272" s="3" t="n">
         <v>2024</v>
       </c>
@@ -8255,7 +8255,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="273" ht="16" customHeight="1">
+    <row r="273" ht="18" customHeight="1">
       <c r="A273" s="3" t="n">
         <v>2025</v>
       </c>
@@ -8284,7 +8284,7 @@
         <v>33.7</v>
       </c>
     </row>
-    <row r="274" ht="16" customHeight="1">
+    <row r="274" ht="18" customHeight="1">
       <c r="A274" s="3" t="n">
         <v>2024</v>
       </c>
@@ -8313,7 +8313,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="275" ht="16" customHeight="1">
+    <row r="275" ht="18" customHeight="1">
       <c r="A275" s="3" t="n">
         <v>2025</v>
       </c>
@@ -8342,7 +8342,7 @@
         <v>35.9</v>
       </c>
     </row>
-    <row r="276" ht="16" customHeight="1">
+    <row r="276" ht="18" customHeight="1">
       <c r="A276" s="3" t="n">
         <v>2024</v>
       </c>
@@ -8374,7 +8374,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="277" ht="16" customHeight="1">
+    <row r="277" ht="18" customHeight="1">
       <c r="A277" s="3" t="n">
         <v>2025</v>
       </c>
@@ -8406,7 +8406,7 @@
         <v>38.3</v>
       </c>
     </row>
-    <row r="278" ht="16" customHeight="1">
+    <row r="278" ht="18" customHeight="1">
       <c r="A278" s="3" t="n">
         <v>2024</v>
       </c>
@@ -8435,7 +8435,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="279" ht="16" customHeight="1">
+    <row r="279" ht="18" customHeight="1">
       <c r="A279" s="3" t="n">
         <v>2025</v>
       </c>
@@ -8467,7 +8467,7 @@
         <v>36.9</v>
       </c>
     </row>
-    <row r="280" ht="16" customHeight="1">
+    <row r="280" ht="18" customHeight="1">
       <c r="A280" s="3" t="n">
         <v>2024</v>
       </c>
@@ -8496,7 +8496,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="281" ht="16" customHeight="1">
+    <row r="281" ht="18" customHeight="1">
       <c r="A281" s="3" t="n">
         <v>2025</v>
       </c>
@@ -8528,7 +8528,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="282" ht="16" customHeight="1">
+    <row r="282" ht="18" customHeight="1">
       <c r="A282" s="3" t="n">
         <v>2024</v>
       </c>
@@ -8557,7 +8557,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="283" ht="16" customHeight="1">
+    <row r="283" ht="18" customHeight="1">
       <c r="A283" s="3" t="n">
         <v>2025</v>
       </c>
@@ -8583,7 +8583,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="284" ht="16" customHeight="1">
+    <row r="284" ht="18" customHeight="1">
       <c r="A284" s="3" t="n">
         <v>2024</v>
       </c>
@@ -8612,7 +8612,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="285" ht="16" customHeight="1">
+    <row r="285" ht="18" customHeight="1">
       <c r="A285" s="3" t="n">
         <v>2025</v>
       </c>
@@ -8641,7 +8641,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="286" ht="16" customHeight="1">
+    <row r="286" ht="18" customHeight="1">
       <c r="A286" s="3" t="n">
         <v>2024</v>
       </c>
@@ -8670,7 +8670,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="287" ht="16" customHeight="1">
+    <row r="287" ht="18" customHeight="1">
       <c r="A287" s="3" t="n">
         <v>2025</v>
       </c>
@@ -8696,7 +8696,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="288" ht="16" customHeight="1">
+    <row r="288" ht="18" customHeight="1">
       <c r="A288" s="3" t="n">
         <v>2024</v>
       </c>
@@ -8728,7 +8728,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="289" ht="16" customHeight="1">
+    <row r="289" ht="18" customHeight="1">
       <c r="A289" s="3" t="n">
         <v>2025</v>
       </c>
@@ -8760,7 +8760,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="290" ht="16" customHeight="1">
+    <row r="290" ht="18" customHeight="1">
       <c r="A290" s="3" t="n">
         <v>2024</v>
       </c>
@@ -8786,7 +8786,7 @@
         <v>54.3</v>
       </c>
     </row>
-    <row r="291" ht="16" customHeight="1">
+    <row r="291" ht="18" customHeight="1">
       <c r="A291" s="3" t="n">
         <v>2025</v>
       </c>
@@ -8815,7 +8815,7 @@
         <v>2964</v>
       </c>
     </row>
-    <row r="292" ht="16" customHeight="1">
+    <row r="292" ht="18" customHeight="1">
       <c r="A292" s="3" t="n">
         <v>2024</v>
       </c>
@@ -8841,7 +8841,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="293" ht="16" customHeight="1">
+    <row r="293" ht="18" customHeight="1">
       <c r="A293" s="3" t="n">
         <v>2025</v>
       </c>
@@ -8867,7 +8867,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="294" ht="16" customHeight="1">
+    <row r="294" ht="18" customHeight="1">
       <c r="A294" s="3" t="n">
         <v>2024</v>
       </c>
@@ -8890,7 +8890,7 @@
         <v>48.6</v>
       </c>
     </row>
-    <row r="295" ht="16" customHeight="1">
+    <row r="295" ht="18" customHeight="1">
       <c r="A295" s="3" t="n">
         <v>2025</v>
       </c>
@@ -8919,7 +8919,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="296" ht="16" customHeight="1">
+    <row r="296" ht="18" customHeight="1">
       <c r="A296" s="3" t="n">
         <v>2024</v>
       </c>
@@ -8945,7 +8945,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="297" ht="16" customHeight="1">
+    <row r="297" ht="18" customHeight="1">
       <c r="A297" s="3" t="n">
         <v>2025</v>
       </c>
@@ -8974,7 +8974,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="298" ht="16" customHeight="1">
+    <row r="298" ht="18" customHeight="1">
       <c r="A298" s="3" t="n">
         <v>2024</v>
       </c>
@@ -9000,7 +9000,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="299" ht="16" customHeight="1">
+    <row r="299" ht="18" customHeight="1">
       <c r="A299" s="3" t="n">
         <v>2025</v>
       </c>
@@ -9026,7 +9026,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="300" ht="16" customHeight="1">
+    <row r="300" ht="18" customHeight="1">
       <c r="A300" s="3" t="n">
         <v>2024</v>
       </c>
@@ -9055,7 +9055,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="301" ht="16" customHeight="1">
+    <row r="301" ht="18" customHeight="1">
       <c r="A301" s="3" t="n">
         <v>2025</v>
       </c>
@@ -9084,7 +9084,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="302" ht="16" customHeight="1">
+    <row r="302" ht="18" customHeight="1">
       <c r="A302" s="3" t="n">
         <v>2024</v>
       </c>
@@ -9113,7 +9113,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="303" ht="16" customHeight="1">
+    <row r="303" ht="18" customHeight="1">
       <c r="A303" s="3" t="n">
         <v>2025</v>
       </c>
@@ -9139,7 +9139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="304" ht="16" customHeight="1">
+    <row r="304" ht="18" customHeight="1">
       <c r="A304" s="3" t="n">
         <v>2024</v>
       </c>
@@ -9171,7 +9171,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="305" ht="16" customHeight="1">
+    <row r="305" ht="18" customHeight="1">
       <c r="A305" s="3" t="n">
         <v>2025</v>
       </c>
@@ -9203,7 +9203,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="306" ht="16" customHeight="1">
+    <row r="306" ht="18" customHeight="1">
       <c r="A306" s="3" t="n">
         <v>2024</v>
       </c>
@@ -9232,7 +9232,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="307" ht="16" customHeight="1">
+    <row r="307" ht="18" customHeight="1">
       <c r="A307" s="3" t="n">
         <v>2025</v>
       </c>
@@ -9261,7 +9261,7 @@
         <v>30.9</v>
       </c>
     </row>
-    <row r="308" ht="16" customHeight="1">
+    <row r="308" ht="18" customHeight="1">
       <c r="A308" s="3" t="n">
         <v>2024</v>
       </c>
@@ -9287,7 +9287,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="309" ht="16" customHeight="1">
+    <row r="309" ht="18" customHeight="1">
       <c r="A309" s="3" t="n">
         <v>2025</v>
       </c>
@@ -9313,7 +9313,7 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="310" ht="16" customHeight="1">
+    <row r="310" ht="18" customHeight="1">
       <c r="A310" s="3" t="n">
         <v>2024</v>
       </c>
@@ -9339,7 +9339,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="311" ht="16" customHeight="1">
+    <row r="311" ht="18" customHeight="1">
       <c r="A311" s="3" t="n">
         <v>2025</v>
       </c>
@@ -9368,7 +9368,7 @@
         <v>31.9</v>
       </c>
     </row>
-    <row r="312" ht="16" customHeight="1">
+    <row r="312" ht="18" customHeight="1">
       <c r="A312" s="3" t="n">
         <v>2024</v>
       </c>
@@ -9397,7 +9397,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="313" ht="16" customHeight="1">
+    <row r="313" ht="18" customHeight="1">
       <c r="A313" s="3" t="n">
         <v>2025</v>
       </c>
@@ -9426,7 +9426,7 @@
         <v>36.8</v>
       </c>
     </row>
-    <row r="314" ht="16" customHeight="1">
+    <row r="314" ht="18" customHeight="1">
       <c r="A314" s="3" t="n">
         <v>2024</v>
       </c>
@@ -9458,7 +9458,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="315" ht="16" customHeight="1">
+    <row r="315" ht="18" customHeight="1">
       <c r="A315" s="3" t="n">
         <v>2025</v>
       </c>
@@ -9487,7 +9487,7 @@
         <v>39.3</v>
       </c>
     </row>
-    <row r="316" ht="16" customHeight="1">
+    <row r="316" ht="18" customHeight="1">
       <c r="A316" s="3" t="n">
         <v>2024</v>
       </c>
@@ -9513,7 +9513,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="317" ht="16" customHeight="1">
+    <row r="317" ht="18" customHeight="1">
       <c r="A317" s="3" t="n">
         <v>2025</v>
       </c>
@@ -9545,7 +9545,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="318" ht="16" customHeight="1">
+    <row r="318" ht="18" customHeight="1">
       <c r="A318" s="3" t="n">
         <v>2024</v>
       </c>
@@ -9571,7 +9571,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="319" ht="16" customHeight="1">
+    <row r="319" ht="18" customHeight="1">
       <c r="A319" s="3" t="n">
         <v>2025</v>
       </c>
@@ -9597,7 +9597,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="320" ht="16" customHeight="1">
+    <row r="320" ht="18" customHeight="1">
       <c r="A320" s="3" t="n">
         <v>2024</v>
       </c>
@@ -9623,7 +9623,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="321" ht="16" customHeight="1">
+    <row r="321" ht="18" customHeight="1">
       <c r="A321" s="3" t="n">
         <v>2025</v>
       </c>
@@ -9652,7 +9652,7 @@
         <v>40.4</v>
       </c>
     </row>
-    <row r="322" ht="16" customHeight="1">
+    <row r="322" ht="18" customHeight="1">
       <c r="A322" s="3" t="n">
         <v>2024</v>
       </c>
@@ -9678,7 +9678,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="323" ht="16" customHeight="1">
+    <row r="323" ht="18" customHeight="1">
       <c r="A323" s="3" t="n">
         <v>2025</v>
       </c>
@@ -9707,7 +9707,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="324" ht="16" customHeight="1">
+    <row r="324" ht="18" customHeight="1">
       <c r="A324" s="3" t="n">
         <v>2024</v>
       </c>
@@ -9730,7 +9730,7 @@
         <v>52.3</v>
       </c>
     </row>
-    <row r="325" ht="16" customHeight="1">
+    <row r="325" ht="18" customHeight="1">
       <c r="A325" s="3" t="n">
         <v>2025</v>
       </c>
@@ -9753,7 +9753,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="326" ht="16" customHeight="1">
+    <row r="326" ht="18" customHeight="1">
       <c r="A326" s="3" t="n">
         <v>2024</v>
       </c>
@@ -9776,7 +9776,7 @@
         <v>58.4</v>
       </c>
     </row>
-    <row r="327" ht="16" customHeight="1">
+    <row r="327" ht="18" customHeight="1">
       <c r="A327" s="3" t="n">
         <v>2025</v>
       </c>
@@ -9802,7 +9802,7 @@
         <v>34.2</v>
       </c>
     </row>
-    <row r="328" ht="16" customHeight="1">
+    <row r="328" ht="18" customHeight="1">
       <c r="A328" s="3" t="n">
         <v>2024</v>
       </c>
@@ -9825,7 +9825,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="329" ht="16" customHeight="1">
+    <row r="329" ht="18" customHeight="1">
       <c r="A329" s="3" t="n">
         <v>2025</v>
       </c>
@@ -9851,7 +9851,7 @@
         <v>2397</v>
       </c>
     </row>
-    <row r="330" ht="16" customHeight="1">
+    <row r="330" ht="18" customHeight="1">
       <c r="A330" s="3" t="n">
         <v>2024</v>
       </c>
@@ -9877,7 +9877,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="331" ht="16" customHeight="1">
+    <row r="331" ht="18" customHeight="1">
       <c r="A331" s="3" t="n">
         <v>2025</v>
       </c>
@@ -9906,7 +9906,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="332" ht="16" customHeight="1">
+    <row r="332" ht="18" customHeight="1">
       <c r="A332" s="3" t="n">
         <v>2024</v>
       </c>
@@ -9932,7 +9932,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="333" ht="16" customHeight="1">
+    <row r="333" ht="18" customHeight="1">
       <c r="A333" s="3" t="n">
         <v>2025</v>
       </c>
@@ -9961,7 +9961,7 @@
         <v>33.9</v>
       </c>
     </row>
-    <row r="334" ht="16" customHeight="1">
+    <row r="334" ht="18" customHeight="1">
       <c r="A334" s="3" t="n">
         <v>2024</v>
       </c>
@@ -9987,7 +9987,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="335" ht="16" customHeight="1">
+    <row r="335" ht="18" customHeight="1">
       <c r="A335" s="3" t="n">
         <v>2025</v>
       </c>
@@ -10013,7 +10013,7 @@
         <v>18.1</v>
       </c>
     </row>
-    <row r="336" ht="16" customHeight="1">
+    <row r="336" ht="18" customHeight="1">
       <c r="A336" s="3" t="n">
         <v>2024</v>
       </c>
@@ -10045,7 +10045,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="337" ht="16" customHeight="1">
+    <row r="337" ht="18" customHeight="1">
       <c r="A337" s="3" t="n">
         <v>2025</v>
       </c>
@@ -10077,7 +10077,7 @@
         <v>31.7</v>
       </c>
     </row>
-    <row r="338" ht="16" customHeight="1">
+    <row r="338" ht="18" customHeight="1">
       <c r="A338" s="3" t="n">
         <v>2024</v>
       </c>
@@ -10106,7 +10106,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="339" ht="16" customHeight="1">
+    <row r="339" ht="18" customHeight="1">
       <c r="A339" s="3" t="n">
         <v>2025</v>
       </c>
@@ -10138,7 +10138,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="340" ht="16" customHeight="1">
+    <row r="340" ht="18" customHeight="1">
       <c r="A340" s="3" t="n">
         <v>2024</v>
       </c>
@@ -10167,7 +10167,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="341" ht="16" customHeight="1">
+    <row r="341" ht="18" customHeight="1">
       <c r="A341" s="3" t="n">
         <v>2025</v>
       </c>
@@ -10199,7 +10199,7 @@
         <v>28.9</v>
       </c>
     </row>
-    <row r="342" ht="16" customHeight="1">
+    <row r="342" ht="18" customHeight="1">
       <c r="A342" s="3" t="n">
         <v>2024</v>
       </c>
@@ -10228,7 +10228,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="343" ht="16" customHeight="1">
+    <row r="343" ht="18" customHeight="1">
       <c r="A343" s="3" t="n">
         <v>2025</v>
       </c>
@@ -10260,7 +10260,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="344" ht="16" customHeight="1">
+    <row r="344" ht="18" customHeight="1">
       <c r="A344" s="3" t="n">
         <v>2024</v>
       </c>
@@ -10292,7 +10292,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="345" ht="16" customHeight="1">
+    <row r="345" ht="18" customHeight="1">
       <c r="A345" s="3" t="n">
         <v>2025</v>
       </c>
@@ -10324,7 +10324,7 @@
         <v>34.2</v>
       </c>
     </row>
-    <row r="346" ht="16" customHeight="1">
+    <row r="346" ht="18" customHeight="1">
       <c r="A346" s="3" t="n">
         <v>2024</v>
       </c>
@@ -10356,7 +10356,7 @@
         <v>19.1</v>
       </c>
     </row>
-    <row r="347" ht="16" customHeight="1">
+    <row r="347" ht="18" customHeight="1">
       <c r="A347" s="3" t="n">
         <v>2025</v>
       </c>
@@ -10388,7 +10388,7 @@
         <v>32.8</v>
       </c>
     </row>
-    <row r="348" ht="16" customHeight="1">
+    <row r="348" ht="18" customHeight="1">
       <c r="A348" s="3" t="n">
         <v>2024</v>
       </c>
@@ -10420,7 +10420,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="349" ht="16" customHeight="1">
+    <row r="349" ht="18" customHeight="1">
       <c r="A349" s="3" t="n">
         <v>2025</v>
       </c>
@@ -10452,7 +10452,7 @@
         <v>29.2</v>
       </c>
     </row>
-    <row r="350" ht="16" customHeight="1">
+    <row r="350" ht="18" customHeight="1">
       <c r="A350" s="3" t="n">
         <v>2024</v>
       </c>
@@ -10481,7 +10481,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="351" ht="16" customHeight="1">
+    <row r="351" ht="18" customHeight="1">
       <c r="A351" s="3" t="n">
         <v>2025</v>
       </c>
@@ -10510,7 +10510,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="352" ht="16" customHeight="1">
+    <row r="352" ht="18" customHeight="1">
       <c r="A352" s="3" t="n">
         <v>2024</v>
       </c>
@@ -10542,7 +10542,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="353" ht="16" customHeight="1">
+    <row r="353" ht="18" customHeight="1">
       <c r="A353" s="3" t="n">
         <v>2025</v>
       </c>
@@ -10574,7 +10574,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="354" ht="16" customHeight="1">
+    <row r="354" ht="18" customHeight="1">
       <c r="A354" s="3" t="n">
         <v>2024</v>
       </c>
@@ -10606,7 +10606,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="355" ht="16" customHeight="1">
+    <row r="355" ht="18" customHeight="1">
       <c r="A355" s="3" t="n">
         <v>2025</v>
       </c>
@@ -10635,7 +10635,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="356" ht="16" customHeight="1">
+    <row r="356" ht="18" customHeight="1">
       <c r="A356" s="3" t="n">
         <v>2024</v>
       </c>
@@ -10667,7 +10667,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="357" ht="16" customHeight="1">
+    <row r="357" ht="18" customHeight="1">
       <c r="A357" s="3" t="n">
         <v>2025</v>
       </c>
@@ -10699,7 +10699,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="358" ht="16" customHeight="1">
+    <row r="358" ht="18" customHeight="1">
       <c r="A358" s="3" t="n">
         <v>2024</v>
       </c>
@@ -10728,7 +10728,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="359" ht="16" customHeight="1">
+    <row r="359" ht="18" customHeight="1">
       <c r="A359" s="3" t="n">
         <v>2025</v>
       </c>
@@ -10757,7 +10757,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="360" ht="16" customHeight="1">
+    <row r="360" ht="18" customHeight="1">
       <c r="A360" s="3" t="n">
         <v>2024</v>
       </c>
@@ -10780,7 +10780,7 @@
         <v>62.4</v>
       </c>
     </row>
-    <row r="361" ht="16" customHeight="1">
+    <row r="361" ht="18" customHeight="1">
       <c r="A361" s="3" t="n">
         <v>2025</v>
       </c>
@@ -10803,7 +10803,7 @@
         <v>56.2</v>
       </c>
     </row>
-    <row r="362" ht="16" customHeight="1">
+    <row r="362" ht="18" customHeight="1">
       <c r="A362" s="3" t="n">
         <v>2024</v>
       </c>
@@ -10826,7 +10826,7 @@
         <v>56.5</v>
       </c>
     </row>
-    <row r="363" ht="16" customHeight="1">
+    <row r="363" ht="18" customHeight="1">
       <c r="A363" s="3" t="n">
         <v>2025</v>
       </c>
@@ -10849,7 +10849,7 @@
         <v>52.2</v>
       </c>
     </row>
-    <row r="364" ht="16" customHeight="1">
+    <row r="364" ht="18" customHeight="1">
       <c r="A364" s="3" t="n">
         <v>2024</v>
       </c>
@@ -10872,7 +10872,7 @@
         <v>29.3</v>
       </c>
     </row>
-    <row r="365" ht="16" customHeight="1">
+    <row r="365" ht="18" customHeight="1">
       <c r="A365" s="3" t="n">
         <v>2025</v>
       </c>
@@ -10895,7 +10895,7 @@
         <v>44.3</v>
       </c>
     </row>
-    <row r="366" ht="16" customHeight="1">
+    <row r="366" ht="18" customHeight="1">
       <c r="A366" s="3" t="n">
         <v>2024</v>
       </c>
@@ -10918,7 +10918,7 @@
         <v>59.1</v>
       </c>
     </row>
-    <row r="367" ht="16" customHeight="1">
+    <row r="367" ht="18" customHeight="1">
       <c r="A367" s="3" t="n">
         <v>2025</v>
       </c>
@@ -10941,7 +10941,7 @@
         <v>57.4</v>
       </c>
     </row>
-    <row r="368" ht="16" customHeight="1">
+    <row r="368" ht="18" customHeight="1">
       <c r="A368" s="3" t="n">
         <v>2024</v>
       </c>
@@ -10967,7 +10967,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="369" ht="16" customHeight="1">
+    <row r="369" ht="18" customHeight="1">
       <c r="A369" s="3" t="n">
         <v>2025</v>
       </c>
@@ -10993,7 +10993,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="370" ht="16" customHeight="1">
+    <row r="370" ht="18" customHeight="1">
       <c r="A370" s="3" t="n">
         <v>2024</v>
       </c>
@@ -11019,7 +11019,7 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="371" ht="16" customHeight="1">
+    <row r="371" ht="18" customHeight="1">
       <c r="A371" s="3" t="n">
         <v>2025</v>
       </c>
@@ -11045,7 +11045,7 @@
         <v>36.7</v>
       </c>
     </row>
-    <row r="372" ht="16" customHeight="1">
+    <row r="372" ht="18" customHeight="1">
       <c r="A372" s="3" t="n">
         <v>2024</v>
       </c>
@@ -11071,7 +11071,7 @@
         <v>2403</v>
       </c>
     </row>
-    <row r="373" ht="16" customHeight="1">
+    <row r="373" ht="18" customHeight="1">
       <c r="A373" s="3" t="n">
         <v>2025</v>
       </c>
@@ -11094,7 +11094,7 @@
         <v>56.8</v>
       </c>
     </row>
-    <row r="374" ht="16" customHeight="1">
+    <row r="374" ht="18" customHeight="1">
       <c r="A374" s="3" t="n">
         <v>2024</v>
       </c>
@@ -11120,7 +11120,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="375" ht="16" customHeight="1">
+    <row r="375" ht="18" customHeight="1">
       <c r="A375" s="3" t="n">
         <v>2025</v>
       </c>
@@ -11146,7 +11146,7 @@
         <v>2384</v>
       </c>
     </row>
-    <row r="376" ht="16" customHeight="1">
+    <row r="376" ht="18" customHeight="1">
       <c r="A376" s="3" t="n">
         <v>2024</v>
       </c>
@@ -11172,7 +11172,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="377" ht="16" customHeight="1">
+    <row r="377" ht="18" customHeight="1">
       <c r="A377" s="3" t="n">
         <v>2025</v>
       </c>
@@ -11198,7 +11198,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="378" ht="16" customHeight="1">
+    <row r="378" ht="18" customHeight="1">
       <c r="A378" s="3" t="n">
         <v>2024</v>
       </c>
@@ -11224,7 +11224,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="379" ht="16" customHeight="1">
+    <row r="379" ht="18" customHeight="1">
       <c r="A379" s="3" t="n">
         <v>2025</v>
       </c>
@@ -11253,7 +11253,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="380" ht="16" customHeight="1">
+    <row r="380" ht="18" customHeight="1">
       <c r="A380" s="3" t="n">
         <v>2024</v>
       </c>
@@ -11282,7 +11282,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="381" ht="16" customHeight="1">
+    <row r="381" ht="18" customHeight="1">
       <c r="A381" s="3" t="n">
         <v>2025</v>
       </c>
@@ -11311,7 +11311,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="382" ht="16" customHeight="1">
+    <row r="382" ht="18" customHeight="1">
       <c r="A382" s="3" t="n">
         <v>2024</v>
       </c>
@@ -11340,7 +11340,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="383" ht="16" customHeight="1">
+    <row r="383" ht="18" customHeight="1">
       <c r="A383" s="3" t="n">
         <v>2025</v>
       </c>
@@ -11369,7 +11369,7 @@
         <v>30.4</v>
       </c>
     </row>
-    <row r="384" ht="16" customHeight="1">
+    <row r="384" ht="18" customHeight="1">
       <c r="A384" s="3" t="n">
         <v>2024</v>
       </c>
@@ -11395,7 +11395,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="385" ht="16" customHeight="1">
+    <row r="385" ht="18" customHeight="1">
       <c r="A385" s="3" t="n">
         <v>2025</v>
       </c>
@@ -11421,7 +11421,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="386" ht="16" customHeight="1">
+    <row r="386" ht="18" customHeight="1">
       <c r="A386" s="3" t="n">
         <v>2024</v>
       </c>
@@ -11450,7 +11450,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="387" ht="16" customHeight="1">
+    <row r="387" ht="18" customHeight="1">
       <c r="A387" s="3" t="n">
         <v>2025</v>
       </c>
@@ -11479,7 +11479,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="388" ht="16" customHeight="1">
+    <row r="388" ht="18" customHeight="1">
       <c r="A388" s="3" t="n">
         <v>2024</v>
       </c>
@@ -11508,7 +11508,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="389" ht="16" customHeight="1">
+    <row r="389" ht="18" customHeight="1">
       <c r="A389" s="3" t="n">
         <v>2025</v>
       </c>
@@ -11537,7 +11537,7 @@
         <v>43.1</v>
       </c>
     </row>
-    <row r="390" ht="16" customHeight="1">
+    <row r="390" ht="18" customHeight="1">
       <c r="A390" s="3" t="n">
         <v>2024</v>
       </c>
@@ -11566,7 +11566,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="391" ht="16" customHeight="1">
+    <row r="391" ht="18" customHeight="1">
       <c r="A391" s="3" t="n">
         <v>2025</v>
       </c>
@@ -11592,7 +11592,7 @@
         <v>43.3</v>
       </c>
     </row>
-    <row r="392" ht="16" customHeight="1">
+    <row r="392" ht="18" customHeight="1">
       <c r="A392" s="3" t="n">
         <v>2024</v>
       </c>
@@ -11618,7 +11618,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="393" ht="16" customHeight="1">
+    <row r="393" ht="18" customHeight="1">
       <c r="A393" s="3" t="n">
         <v>2025</v>
       </c>
@@ -11647,7 +11647,7 @@
         <v>37.9</v>
       </c>
     </row>
-    <row r="394" ht="16" customHeight="1">
+    <row r="394" ht="18" customHeight="1">
       <c r="A394" s="3" t="n">
         <v>2024</v>
       </c>
@@ -11673,7 +11673,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="395" ht="16" customHeight="1">
+    <row r="395" ht="18" customHeight="1">
       <c r="A395" s="3" t="n">
         <v>2025</v>
       </c>
@@ -11702,7 +11702,7 @@
         <v>34.6</v>
       </c>
     </row>
-    <row r="396" ht="16" customHeight="1">
+    <row r="396" ht="18" customHeight="1">
       <c r="A396" s="3" t="n">
         <v>2024</v>
       </c>
@@ -11731,7 +11731,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="397" ht="16" customHeight="1">
+    <row r="397" ht="18" customHeight="1">
       <c r="A397" s="3" t="n">
         <v>2025</v>
       </c>
@@ -11760,7 +11760,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="398" ht="16" customHeight="1">
+    <row r="398" ht="18" customHeight="1">
       <c r="A398" s="3" t="n">
         <v>2024</v>
       </c>
@@ -11783,7 +11783,7 @@
         <v>41.5</v>
       </c>
     </row>
-    <row r="399" ht="16" customHeight="1">
+    <row r="399" ht="18" customHeight="1">
       <c r="A399" s="3" t="n">
         <v>2025</v>
       </c>
@@ -11806,7 +11806,7 @@
         <v>38.9</v>
       </c>
     </row>
-    <row r="400" ht="16" customHeight="1">
+    <row r="400" ht="18" customHeight="1">
       <c r="A400" s="3" t="n">
         <v>2024</v>
       </c>
@@ -11829,7 +11829,7 @@
         <v>55.3</v>
       </c>
     </row>
-    <row r="401" ht="16" customHeight="1">
+    <row r="401" ht="18" customHeight="1">
       <c r="A401" s="3" t="n">
         <v>2025</v>
       </c>
@@ -11852,7 +11852,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="402" ht="16" customHeight="1">
+    <row r="402" ht="18" customHeight="1">
       <c r="A402" s="3" t="n">
         <v>2024</v>
       </c>
@@ -11875,7 +11875,7 @@
         <v>43.2</v>
       </c>
     </row>
-    <row r="403" ht="16" customHeight="1">
+    <row r="403" ht="18" customHeight="1">
       <c r="A403" s="3" t="n">
         <v>2025</v>
       </c>
@@ -11898,7 +11898,7 @@
         <v>42.8</v>
       </c>
     </row>
-    <row r="404" ht="16" customHeight="1">
+    <row r="404" ht="18" customHeight="1">
       <c r="A404" s="3" t="n">
         <v>2024</v>
       </c>
@@ -11918,7 +11918,7 @@
         <v>103.5</v>
       </c>
     </row>
-    <row r="405" ht="16" customHeight="1">
+    <row r="405" ht="18" customHeight="1">
       <c r="A405" s="3" t="n">
         <v>2025</v>
       </c>
@@ -11938,7 +11938,7 @@
         <v>119.2</v>
       </c>
     </row>
-    <row r="406" ht="16" customHeight="1">
+    <row r="406" ht="18" customHeight="1">
       <c r="A406" s="3" t="n">
         <v>2024</v>
       </c>
@@ -11967,7 +11967,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="407" ht="16" customHeight="1">
+    <row r="407" ht="18" customHeight="1">
       <c r="A407" s="3" t="n">
         <v>2025</v>
       </c>
@@ -11996,7 +11996,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="408" ht="16" customHeight="1">
+    <row r="408" ht="18" customHeight="1">
       <c r="A408" s="3" t="n">
         <v>2024</v>
       </c>
@@ -12019,7 +12019,7 @@
         <v>55.3</v>
       </c>
     </row>
-    <row r="409" ht="16" customHeight="1">
+    <row r="409" ht="18" customHeight="1">
       <c r="A409" s="3" t="n">
         <v>2025</v>
       </c>
@@ -12042,7 +12042,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="410" ht="16" customHeight="1">
+    <row r="410" ht="18" customHeight="1">
       <c r="A410" s="3" t="n">
         <v>2024</v>
       </c>
@@ -12065,7 +12065,7 @@
         <v>55.8</v>
       </c>
     </row>
-    <row r="411" ht="16" customHeight="1">
+    <row r="411" ht="18" customHeight="1">
       <c r="A411" s="3" t="n">
         <v>2025</v>
       </c>
@@ -12088,7 +12088,7 @@
         <v>59.7</v>
       </c>
     </row>
-    <row r="412" ht="16" customHeight="1">
+    <row r="412" ht="18" customHeight="1">
       <c r="A412" s="3" t="n">
         <v>2024</v>
       </c>
@@ -12120,7 +12120,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="413" ht="16" customHeight="1">
+    <row r="413" ht="18" customHeight="1">
       <c r="A413" s="3" t="n">
         <v>2025</v>
       </c>
@@ -12152,7 +12152,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="414" ht="16" customHeight="1">
+    <row r="414" ht="18" customHeight="1">
       <c r="A414" s="3" t="n">
         <v>2024</v>
       </c>
@@ -12184,7 +12184,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="415" ht="16" customHeight="1">
+    <row r="415" ht="18" customHeight="1">
       <c r="A415" s="3" t="n">
         <v>2025</v>
       </c>
@@ -12216,7 +12216,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="416" ht="16" customHeight="1">
+    <row r="416" ht="18" customHeight="1">
       <c r="A416" s="3" t="n">
         <v>2024</v>
       </c>
@@ -12242,7 +12242,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="417" ht="16" customHeight="1">
+    <row r="417" ht="18" customHeight="1">
       <c r="A417" s="3" t="n">
         <v>2025</v>
       </c>
@@ -12271,7 +12271,7 @@
         <v>39.2</v>
       </c>
     </row>
-    <row r="418" ht="16" customHeight="1">
+    <row r="418" ht="18" customHeight="1">
       <c r="A418" s="3" t="n">
         <v>2024</v>
       </c>
@@ -12300,7 +12300,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="419" ht="16" customHeight="1">
+    <row r="419" ht="18" customHeight="1">
       <c r="A419" s="3" t="n">
         <v>2025</v>
       </c>
@@ -12329,7 +12329,7 @@
         <v>29.4</v>
       </c>
     </row>
-    <row r="420" ht="16" customHeight="1">
+    <row r="420" ht="18" customHeight="1">
       <c r="A420" s="3" t="n">
         <v>2024</v>
       </c>
@@ -12358,7 +12358,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="421" ht="16" customHeight="1">
+    <row r="421" ht="18" customHeight="1">
       <c r="A421" s="3" t="n">
         <v>2025</v>
       </c>
@@ -12390,7 +12390,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="422" ht="16" customHeight="1">
+    <row r="422" ht="18" customHeight="1">
       <c r="A422" s="3" t="n">
         <v>2024</v>
       </c>
@@ -12416,7 +12416,7 @@
         <v>1799</v>
       </c>
     </row>
-    <row r="423" ht="16" customHeight="1">
+    <row r="423" ht="18" customHeight="1">
       <c r="A423" s="3" t="n">
         <v>2025</v>
       </c>
@@ -12448,7 +12448,7 @@
         <v>37.7</v>
       </c>
     </row>
-    <row r="424" ht="16" customHeight="1">
+    <row r="424" ht="18" customHeight="1">
       <c r="A424" s="3" t="n">
         <v>2024</v>
       </c>
@@ -12474,7 +12474,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="425" ht="16" customHeight="1">
+    <row r="425" ht="18" customHeight="1">
       <c r="A425" s="3" t="n">
         <v>2025</v>
       </c>
@@ -12503,7 +12503,7 @@
         <v>2816</v>
       </c>
     </row>
-    <row r="426" ht="16" customHeight="1">
+    <row r="426" ht="18" customHeight="1">
       <c r="A426" s="3" t="n">
         <v>2024</v>
       </c>
@@ -12532,7 +12532,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="427" ht="16" customHeight="1">
+    <row r="427" ht="18" customHeight="1">
       <c r="A427" s="3" t="n">
         <v>2025</v>
       </c>
@@ -12561,7 +12561,7 @@
         <v>2385</v>
       </c>
     </row>
-    <row r="428" ht="16" customHeight="1">
+    <row r="428" ht="18" customHeight="1">
       <c r="A428" s="3" t="n">
         <v>2024</v>
       </c>
@@ -12593,7 +12593,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="429" ht="16" customHeight="1">
+    <row r="429" ht="18" customHeight="1">
       <c r="A429" s="3" t="n">
         <v>2025</v>
       </c>
@@ -12625,7 +12625,7 @@
         <v>34.4</v>
       </c>
     </row>
-    <row r="430" ht="16" customHeight="1">
+    <row r="430" ht="18" customHeight="1">
       <c r="A430" s="3" t="n">
         <v>2024</v>
       </c>
@@ -12654,7 +12654,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="431" ht="16" customHeight="1">
+    <row r="431" ht="18" customHeight="1">
       <c r="A431" s="3" t="n">
         <v>2025</v>
       </c>
@@ -12686,7 +12686,7 @@
         <v>34.4</v>
       </c>
     </row>
-    <row r="432" ht="16" customHeight="1">
+    <row r="432" ht="18" customHeight="1">
       <c r="A432" s="3" t="n">
         <v>2024</v>
       </c>
@@ -12715,7 +12715,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="433" ht="16" customHeight="1">
+    <row r="433" ht="18" customHeight="1">
       <c r="A433" s="3" t="n">
         <v>2025</v>
       </c>
@@ -12744,7 +12744,7 @@
         <v>44.4</v>
       </c>
     </row>
-    <row r="434" ht="16" customHeight="1">
+    <row r="434" ht="18" customHeight="1">
       <c r="A434" s="3" t="n">
         <v>2024</v>
       </c>
@@ -12776,7 +12776,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="435" ht="16" customHeight="1">
+    <row r="435" ht="18" customHeight="1">
       <c r="A435" s="3" t="n">
         <v>2025</v>
       </c>
@@ -12808,7 +12808,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="436" ht="16" customHeight="1">
+    <row r="436" ht="18" customHeight="1">
       <c r="A436" s="3" t="n">
         <v>2024</v>
       </c>
@@ -12834,7 +12834,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="437" ht="16" customHeight="1">
+    <row r="437" ht="18" customHeight="1">
       <c r="A437" s="3" t="n">
         <v>2025</v>
       </c>
@@ -12863,7 +12863,7 @@
         <v>36.7</v>
       </c>
     </row>
-    <row r="438" ht="16" customHeight="1">
+    <row r="438" ht="18" customHeight="1">
       <c r="A438" s="3" t="n">
         <v>2024</v>
       </c>
@@ -12886,7 +12886,7 @@
         <v>38.8</v>
       </c>
     </row>
-    <row r="439" ht="16" customHeight="1">
+    <row r="439" ht="18" customHeight="1">
       <c r="A439" s="3" t="n">
         <v>2025</v>
       </c>
@@ -12912,7 +12912,7 @@
         <v>32.7</v>
       </c>
     </row>
-    <row r="440" ht="16" customHeight="1">
+    <row r="440" ht="18" customHeight="1">
       <c r="A440" s="3" t="n">
         <v>2024</v>
       </c>
@@ -12932,7 +12932,7 @@
         <v>109.6</v>
       </c>
     </row>
-    <row r="441" ht="16" customHeight="1">
+    <row r="441" ht="18" customHeight="1">
       <c r="A441" s="3" t="n">
         <v>2025</v>
       </c>
@@ -12955,7 +12955,7 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="442" ht="16" customHeight="1">
+    <row r="442" ht="18" customHeight="1">
       <c r="A442" s="3" t="n">
         <v>2024</v>
       </c>
@@ -12978,7 +12978,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="443" ht="16" customHeight="1">
+    <row r="443" ht="18" customHeight="1">
       <c r="A443" s="3" t="n">
         <v>2025</v>
       </c>
@@ -13004,7 +13004,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="444" ht="16" customHeight="1">
+    <row r="444" ht="18" customHeight="1">
       <c r="A444" s="3" t="n">
         <v>2024</v>
       </c>
@@ -13030,7 +13030,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="445" ht="16" customHeight="1">
+    <row r="445" ht="18" customHeight="1">
       <c r="A445" s="3" t="n">
         <v>2025</v>
       </c>
@@ -13059,7 +13059,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="446" ht="16" customHeight="1">
+    <row r="446" ht="18" customHeight="1">
       <c r="A446" s="3" t="n">
         <v>2024</v>
       </c>
@@ -13088,7 +13088,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="447" ht="16" customHeight="1">
+    <row r="447" ht="18" customHeight="1">
       <c r="A447" s="3" t="n">
         <v>2025</v>
       </c>
@@ -13120,7 +13120,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="448" ht="16" customHeight="1">
+    <row r="448" ht="18" customHeight="1">
       <c r="A448" s="3" t="n">
         <v>2024</v>
       </c>
@@ -13152,7 +13152,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="449" ht="16" customHeight="1">
+    <row r="449" ht="18" customHeight="1">
       <c r="A449" s="3" t="n">
         <v>2025</v>
       </c>
@@ -13184,7 +13184,7 @@
         <v>33.1</v>
       </c>
     </row>
-    <row r="450" ht="16" customHeight="1">
+    <row r="450" ht="18" customHeight="1">
       <c r="A450" s="3" t="n">
         <v>2024</v>
       </c>
@@ -13213,7 +13213,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="451" ht="16" customHeight="1">
+    <row r="451" ht="18" customHeight="1">
       <c r="A451" s="3" t="n">
         <v>2025</v>
       </c>
@@ -13242,7 +13242,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="452" ht="16" customHeight="1">
+    <row r="452" ht="18" customHeight="1">
       <c r="A452" s="3" t="n">
         <v>2024</v>
       </c>
@@ -13271,7 +13271,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="453" ht="16" customHeight="1">
+    <row r="453" ht="18" customHeight="1">
       <c r="A453" s="3" t="n">
         <v>2025</v>
       </c>
@@ -13303,7 +13303,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="454" ht="16" customHeight="1">
+    <row r="454" ht="18" customHeight="1">
       <c r="A454" s="3" t="n">
         <v>2024</v>
       </c>
@@ -13329,7 +13329,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="455" ht="16" customHeight="1">
+    <row r="455" ht="18" customHeight="1">
       <c r="A455" s="3" t="n">
         <v>2025</v>
       </c>
@@ -13358,7 +13358,7 @@
         <v>35.3</v>
       </c>
     </row>
-    <row r="456" ht="16" customHeight="1">
+    <row r="456" ht="18" customHeight="1">
       <c r="A456" s="3" t="n">
         <v>2024</v>
       </c>
@@ -13381,7 +13381,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="457" ht="16" customHeight="1">
+    <row r="457" ht="18" customHeight="1">
       <c r="A457" s="3" t="n">
         <v>2025</v>
       </c>
@@ -13404,7 +13404,7 @@
         <v>2525</v>
       </c>
     </row>
-    <row r="458" ht="16" customHeight="1">
+    <row r="458" ht="18" customHeight="1">
       <c r="A458" s="3" t="n">
         <v>2024</v>
       </c>
@@ -13430,7 +13430,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="459" ht="16" customHeight="1">
+    <row r="459" ht="18" customHeight="1">
       <c r="A459" s="3" t="n">
         <v>2025</v>
       </c>
@@ -13459,7 +13459,7 @@
         <v>33.4</v>
       </c>
     </row>
-    <row r="460" ht="16" customHeight="1">
+    <row r="460" ht="18" customHeight="1">
       <c r="A460" s="3" t="n">
         <v>2024</v>
       </c>
@@ -13482,7 +13482,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="461" ht="16" customHeight="1">
+    <row r="461" ht="18" customHeight="1">
       <c r="A461" s="3" t="n">
         <v>2025</v>
       </c>
@@ -13508,7 +13508,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="462" ht="16" customHeight="1">
+    <row r="462" ht="18" customHeight="1">
       <c r="A462" s="3" t="n">
         <v>2024</v>
       </c>
@@ -13534,7 +13534,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="463" ht="16" customHeight="1">
+    <row r="463" ht="18" customHeight="1">
       <c r="A463" s="3" t="n">
         <v>2025</v>
       </c>
@@ -13557,7 +13557,7 @@
         <v>3086</v>
       </c>
     </row>
-    <row r="464" ht="16" customHeight="1">
+    <row r="464" ht="18" customHeight="1">
       <c r="A464" s="3" t="n">
         <v>2024</v>
       </c>
@@ -13586,7 +13586,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="465" ht="16" customHeight="1">
+    <row r="465" ht="18" customHeight="1">
       <c r="A465" s="3" t="n">
         <v>2025</v>
       </c>
@@ -13618,7 +13618,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="466" ht="16" customHeight="1">
+    <row r="466" ht="18" customHeight="1">
       <c r="A466" s="3" t="n">
         <v>2024</v>
       </c>
@@ -13650,7 +13650,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="467" ht="16" customHeight="1">
+    <row r="467" ht="18" customHeight="1">
       <c r="A467" s="3" t="n">
         <v>2025</v>
       </c>
@@ -13682,7 +13682,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="468" ht="16" customHeight="1">
+    <row r="468" ht="18" customHeight="1">
       <c r="A468" s="3" t="n">
         <v>2024</v>
       </c>
@@ -13708,7 +13708,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="469" ht="16" customHeight="1">
+    <row r="469" ht="18" customHeight="1">
       <c r="A469" s="3" t="n">
         <v>2025</v>
       </c>
@@ -13734,7 +13734,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="470" ht="16" customHeight="1">
+    <row r="470" ht="18" customHeight="1">
       <c r="A470" s="3" t="n">
         <v>2024</v>
       </c>
@@ -13760,7 +13760,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="471" ht="16" customHeight="1">
+    <row r="471" ht="18" customHeight="1">
       <c r="A471" s="3" t="n">
         <v>2025</v>
       </c>
@@ -13786,7 +13786,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="472" ht="16" customHeight="1">
+    <row r="472" ht="18" customHeight="1">
       <c r="A472" s="3" t="n">
         <v>2024</v>
       </c>
@@ -13812,7 +13812,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="473" ht="16" customHeight="1">
+    <row r="473" ht="18" customHeight="1">
       <c r="A473" s="3" t="n">
         <v>2025</v>
       </c>
@@ -13841,7 +13841,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="474" ht="16" customHeight="1">
+    <row r="474" ht="18" customHeight="1">
       <c r="A474" s="3" t="n">
         <v>2024</v>
       </c>
@@ -13864,7 +13864,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="475" ht="16" customHeight="1">
+    <row r="475" ht="18" customHeight="1">
       <c r="A475" s="3" t="n">
         <v>2025</v>
       </c>
@@ -13887,7 +13887,7 @@
         <v>48.5</v>
       </c>
     </row>
-    <row r="476" ht="16" customHeight="1">
+    <row r="476" ht="18" customHeight="1">
       <c r="A476" s="3" t="n">
         <v>2024</v>
       </c>
@@ -13910,7 +13910,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="477" ht="16" customHeight="1">
+    <row r="477" ht="18" customHeight="1">
       <c r="A477" s="3" t="n">
         <v>2025</v>
       </c>
@@ -13933,7 +13933,7 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="478" ht="16" customHeight="1">
+    <row r="478" ht="18" customHeight="1">
       <c r="A478" s="3" t="n">
         <v>2024</v>
       </c>
@@ -13962,7 +13962,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="479" ht="16" customHeight="1">
+    <row r="479" ht="18" customHeight="1">
       <c r="A479" s="3" t="n">
         <v>2025</v>
       </c>
@@ -13994,7 +13994,7 @@
         <v>34.6</v>
       </c>
     </row>
-    <row r="480" ht="16" customHeight="1">
+    <row r="480" ht="18" customHeight="1">
       <c r="A480" s="3" t="n">
         <v>2024</v>
       </c>
@@ -14023,7 +14023,7 @@
         <v>2446</v>
       </c>
     </row>
-    <row r="481" ht="16" customHeight="1">
+    <row r="481" ht="18" customHeight="1">
       <c r="A481" s="3" t="n">
         <v>2025</v>
       </c>
@@ -14055,7 +14055,7 @@
         <v>38.3</v>
       </c>
     </row>
-    <row r="482" ht="16" customHeight="1">
+    <row r="482" ht="18" customHeight="1">
       <c r="A482" s="3" t="n">
         <v>2024</v>
       </c>
@@ -14081,7 +14081,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="483" ht="16" customHeight="1">
+    <row r="483" ht="18" customHeight="1">
       <c r="A483" s="3" t="n">
         <v>2025</v>
       </c>
@@ -14107,7 +14107,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="484" ht="16" customHeight="1">
+    <row r="484" ht="18" customHeight="1">
       <c r="A484" s="3" t="n">
         <v>2024</v>
       </c>
@@ -14133,7 +14133,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="485" ht="16" customHeight="1">
+    <row r="485" ht="18" customHeight="1">
       <c r="A485" s="3" t="n">
         <v>2025</v>
       </c>
@@ -14162,7 +14162,7 @@
         <v>34.9</v>
       </c>
     </row>
-    <row r="486" ht="16" customHeight="1">
+    <row r="486" ht="18" customHeight="1">
       <c r="A486" s="3" t="n">
         <v>2024</v>
       </c>
@@ -14188,7 +14188,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="487" ht="16" customHeight="1">
+    <row r="487" ht="18" customHeight="1">
       <c r="A487" s="3" t="n">
         <v>2025</v>
       </c>
@@ -14217,7 +14217,7 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="488" ht="16" customHeight="1">
+    <row r="488" ht="18" customHeight="1">
       <c r="A488" s="3" t="n">
         <v>2024</v>
       </c>
@@ -14243,7 +14243,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="489" ht="16" customHeight="1">
+    <row r="489" ht="18" customHeight="1">
       <c r="A489" s="3" t="n">
         <v>2025</v>
       </c>
@@ -14269,7 +14269,7 @@
         <v>2576</v>
       </c>
     </row>
-    <row r="490" ht="16" customHeight="1">
+    <row r="490" ht="18" customHeight="1">
       <c r="A490" s="3" t="n">
         <v>2024</v>
       </c>
@@ -14289,7 +14289,7 @@
         <v>34.6</v>
       </c>
     </row>
-    <row r="491" ht="16" customHeight="1">
+    <row r="491" ht="18" customHeight="1">
       <c r="A491" s="3" t="n">
         <v>2025</v>
       </c>
@@ -14318,7 +14318,7 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="492" ht="16" customHeight="1">
+    <row r="492" ht="18" customHeight="1">
       <c r="A492" s="3" t="n">
         <v>2024</v>
       </c>
@@ -14347,7 +14347,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="493" ht="16" customHeight="1">
+    <row r="493" ht="18" customHeight="1">
       <c r="A493" s="3" t="n">
         <v>2025</v>
       </c>
@@ -14373,7 +14373,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="494" ht="16" customHeight="1">
+    <row r="494" ht="18" customHeight="1">
       <c r="A494" s="3" t="n">
         <v>2024</v>
       </c>
@@ -14396,7 +14396,7 @@
         <v>45.8</v>
       </c>
     </row>
-    <row r="495" ht="16" customHeight="1">
+    <row r="495" ht="18" customHeight="1">
       <c r="A495" s="3" t="n">
         <v>2025</v>
       </c>
@@ -14419,7 +14419,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="496" ht="16" customHeight="1">
+    <row r="496" ht="18" customHeight="1">
       <c r="A496" s="3" t="n">
         <v>2024</v>
       </c>
@@ -14445,7 +14445,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="497" ht="16" customHeight="1">
+    <row r="497" ht="18" customHeight="1">
       <c r="A497" s="3" t="n">
         <v>2025</v>
       </c>
@@ -14471,7 +14471,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="498" ht="16" customHeight="1">
+    <row r="498" ht="18" customHeight="1">
       <c r="A498" s="3" t="n">
         <v>2024</v>
       </c>
@@ -14494,7 +14494,7 @@
         <v>33.7</v>
       </c>
     </row>
-    <row r="499" ht="16" customHeight="1">
+    <row r="499" ht="18" customHeight="1">
       <c r="A499" s="3" t="n">
         <v>2025</v>
       </c>
@@ -14517,7 +14517,7 @@
         <v>40.9</v>
       </c>
     </row>
-    <row r="500" ht="16" customHeight="1">
+    <row r="500" ht="18" customHeight="1">
       <c r="A500" s="3" t="n">
         <v>2024</v>
       </c>
@@ -14546,7 +14546,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="501" ht="16" customHeight="1">
+    <row r="501" ht="18" customHeight="1">
       <c r="A501" s="3" t="n">
         <v>2025</v>
       </c>
@@ -14572,7 +14572,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="502" ht="16" customHeight="1">
+    <row r="502" ht="18" customHeight="1">
       <c r="A502" s="3" t="n">
         <v>2024</v>
       </c>
@@ -14598,7 +14598,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="503" ht="16" customHeight="1">
+    <row r="503" ht="18" customHeight="1">
       <c r="A503" s="3" t="n">
         <v>2025</v>
       </c>
@@ -14627,7 +14627,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="504" ht="16" customHeight="1">
+    <row r="504" ht="18" customHeight="1">
       <c r="A504" s="3" t="n">
         <v>2024</v>
       </c>
@@ -14650,7 +14650,7 @@
         <v>55.5</v>
       </c>
     </row>
-    <row r="505" ht="16" customHeight="1">
+    <row r="505" ht="18" customHeight="1">
       <c r="A505" s="3" t="n">
         <v>2025</v>
       </c>
@@ -14676,7 +14676,7 @@
         <v>39.6</v>
       </c>
     </row>
-    <row r="506" ht="16" customHeight="1">
+    <row r="506" ht="18" customHeight="1">
       <c r="A506" s="3" t="n">
         <v>2024</v>
       </c>
@@ -14699,7 +14699,7 @@
         <v>60.2</v>
       </c>
     </row>
-    <row r="507" ht="16" customHeight="1">
+    <row r="507" ht="18" customHeight="1">
       <c r="A507" s="3" t="n">
         <v>2025</v>
       </c>
@@ -14722,7 +14722,7 @@
         <v>54.7</v>
       </c>
     </row>
-    <row r="508" ht="16" customHeight="1">
+    <row r="508" ht="18" customHeight="1">
       <c r="A508" s="3" t="n">
         <v>2024</v>
       </c>
@@ -14745,7 +14745,7 @@
         <v>47.1</v>
       </c>
     </row>
-    <row r="509" ht="16" customHeight="1">
+    <row r="509" ht="18" customHeight="1">
       <c r="A509" s="3" t="n">
         <v>2025</v>
       </c>
@@ -14768,7 +14768,7 @@
         <v>57.3</v>
       </c>
     </row>
-    <row r="510" ht="16" customHeight="1">
+    <row r="510" ht="18" customHeight="1">
       <c r="A510" s="3" t="n">
         <v>2024</v>
       </c>
@@ -14794,7 +14794,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="511" ht="16" customHeight="1">
+    <row r="511" ht="18" customHeight="1">
       <c r="A511" s="3" t="n">
         <v>2025</v>
       </c>
@@ -14820,7 +14820,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="512" ht="16" customHeight="1">
+    <row r="512" ht="18" customHeight="1">
       <c r="A512" s="3" t="n">
         <v>2024</v>
       </c>
@@ -14846,7 +14846,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="513" ht="16" customHeight="1">
+    <row r="513" ht="18" customHeight="1">
       <c r="A513" s="3" t="n">
         <v>2025</v>
       </c>
@@ -14869,7 +14869,7 @@
         <v>47.8</v>
       </c>
     </row>
-    <row r="514" ht="16" customHeight="1">
+    <row r="514" ht="18" customHeight="1">
       <c r="A514" s="3" t="n">
         <v>2024</v>
       </c>
@@ -14898,7 +14898,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="515" ht="16" customHeight="1">
+    <row r="515" ht="18" customHeight="1">
       <c r="A515" s="3" t="n">
         <v>2025</v>
       </c>
@@ -14927,7 +14927,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="516" ht="16" customHeight="1">
+    <row r="516" ht="18" customHeight="1">
       <c r="A516" s="3" t="n">
         <v>2024</v>
       </c>
@@ -14956,7 +14956,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="517" ht="16" customHeight="1">
+    <row r="517" ht="18" customHeight="1">
       <c r="A517" s="3" t="n">
         <v>2025</v>
       </c>
@@ -14985,7 +14985,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="518" ht="16" customHeight="1">
+    <row r="518" ht="18" customHeight="1">
       <c r="A518" s="3" t="n">
         <v>2024</v>
       </c>
@@ -15014,7 +15014,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="519" ht="16" customHeight="1">
+    <row r="519" ht="18" customHeight="1">
       <c r="A519" s="3" t="n">
         <v>2025</v>
       </c>
@@ -15043,7 +15043,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="520" ht="16" customHeight="1">
+    <row r="520" ht="18" customHeight="1">
       <c r="A520" s="3" t="n">
         <v>2024</v>
       </c>
@@ -15066,7 +15066,7 @@
         <v>39.8</v>
       </c>
     </row>
-    <row r="521" ht="16" customHeight="1">
+    <row r="521" ht="18" customHeight="1">
       <c r="A521" s="3" t="n">
         <v>2025</v>
       </c>
@@ -15092,7 +15092,7 @@
         <v>9.800000000000001</v>
       </c>
     </row>
-    <row r="522" ht="16" customHeight="1">
+    <row r="522" ht="18" customHeight="1">
       <c r="A522" s="3" t="n">
         <v>2024</v>
       </c>
@@ -15118,7 +15118,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="523" ht="16" customHeight="1">
+    <row r="523" ht="18" customHeight="1">
       <c r="A523" s="3" t="n">
         <v>2025</v>
       </c>
@@ -15141,7 +15141,7 @@
         <v>51.3</v>
       </c>
     </row>
-    <row r="524" ht="16" customHeight="1">
+    <row r="524" ht="18" customHeight="1">
       <c r="A524" s="3" t="n">
         <v>2024</v>
       </c>
@@ -15167,7 +15167,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="525" ht="16" customHeight="1">
+    <row r="525" ht="18" customHeight="1">
       <c r="A525" s="3" t="n">
         <v>2025</v>
       </c>
@@ -15193,7 +15193,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="526" ht="16" customHeight="1">
+    <row r="526" ht="18" customHeight="1">
       <c r="A526" s="3" t="n">
         <v>2024</v>
       </c>
@@ -15219,7 +15219,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="527" ht="16" customHeight="1">
+    <row r="527" ht="18" customHeight="1">
       <c r="A527" s="3" t="n">
         <v>2025</v>
       </c>
@@ -15245,7 +15245,7 @@
         <v>32.8</v>
       </c>
     </row>
-    <row r="528" ht="16" customHeight="1">
+    <row r="528" ht="18" customHeight="1">
       <c r="A528" s="3" t="n">
         <v>2024</v>
       </c>
@@ -15274,7 +15274,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="529" ht="16" customHeight="1">
+    <row r="529" ht="18" customHeight="1">
       <c r="A529" s="3" t="n">
         <v>2025</v>
       </c>
@@ -15303,7 +15303,7 @@
         <v>39.9</v>
       </c>
     </row>
-    <row r="530" ht="16" customHeight="1">
+    <row r="530" ht="18" customHeight="1">
       <c r="A530" s="3" t="n">
         <v>2024</v>
       </c>
@@ -15326,7 +15326,7 @@
         <v>57.4</v>
       </c>
     </row>
-    <row r="531" ht="16" customHeight="1">
+    <row r="531" ht="18" customHeight="1">
       <c r="A531" s="3" t="n">
         <v>2025</v>
       </c>
@@ -15349,7 +15349,7 @@
         <v>54.5</v>
       </c>
     </row>
-    <row r="532" ht="16" customHeight="1">
+    <row r="532" ht="18" customHeight="1">
       <c r="A532" s="3" t="n">
         <v>2024</v>
       </c>
@@ -15372,7 +15372,7 @@
         <v>52.7</v>
       </c>
     </row>
-    <row r="533" ht="16" customHeight="1">
+    <row r="533" ht="18" customHeight="1">
       <c r="A533" s="3" t="n">
         <v>2025</v>
       </c>
@@ -15401,7 +15401,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="534" ht="16" customHeight="1">
+    <row r="534" ht="18" customHeight="1">
       <c r="A534" s="3" t="n">
         <v>2024</v>
       </c>
@@ -15424,7 +15424,7 @@
         <v>52.4</v>
       </c>
     </row>
-    <row r="535" ht="16" customHeight="1">
+    <row r="535" ht="18" customHeight="1">
       <c r="A535" s="3" t="n">
         <v>2025</v>
       </c>
@@ -15447,7 +15447,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="536" ht="16" customHeight="1">
+    <row r="536" ht="18" customHeight="1">
       <c r="A536" s="3" t="n">
         <v>2024</v>
       </c>
@@ -15473,7 +15473,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="537" ht="16" customHeight="1">
+    <row r="537" ht="18" customHeight="1">
       <c r="A537" s="3" t="n">
         <v>2025</v>
       </c>
@@ -15499,7 +15499,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="538" ht="16" customHeight="1">
+    <row r="538" ht="18" customHeight="1">
       <c r="A538" s="3" t="n">
         <v>2024</v>
       </c>
@@ -15525,7 +15525,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="539" ht="16" customHeight="1">
+    <row r="539" ht="18" customHeight="1">
       <c r="A539" s="3" t="n">
         <v>2025</v>
       </c>
@@ -15551,7 +15551,7 @@
         <v>2073</v>
       </c>
     </row>
-    <row r="540" ht="16" customHeight="1">
+    <row r="540" ht="18" customHeight="1">
       <c r="A540" s="3" t="n">
         <v>2024</v>
       </c>
@@ -15574,7 +15574,7 @@
         <v>33.7</v>
       </c>
     </row>
-    <row r="541" ht="16" customHeight="1">
+    <row r="541" ht="18" customHeight="1">
       <c r="A541" s="3" t="n">
         <v>2025</v>
       </c>
@@ -15597,7 +15597,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="542" ht="16" customHeight="1">
+    <row r="542" ht="18" customHeight="1">
       <c r="A542" s="3" t="n">
         <v>2024</v>
       </c>
@@ -15620,7 +15620,7 @@
         <v>39.4</v>
       </c>
     </row>
-    <row r="543" ht="16" customHeight="1">
+    <row r="543" ht="18" customHeight="1">
       <c r="A543" s="3" t="n">
         <v>2025</v>
       </c>
@@ -15646,7 +15646,7 @@
         <v>2058</v>
       </c>
     </row>
-    <row r="544" ht="16" customHeight="1">
+    <row r="544" ht="18" customHeight="1">
       <c r="A544" s="3" t="n">
         <v>2024</v>
       </c>
@@ -15672,7 +15672,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="545" ht="16" customHeight="1">
+    <row r="545" ht="18" customHeight="1">
       <c r="A545" s="3" t="n">
         <v>2025</v>
       </c>
@@ -15698,7 +15698,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="546" ht="16" customHeight="1">
+    <row r="546" ht="18" customHeight="1">
       <c r="A546" s="3" t="n">
         <v>2024</v>
       </c>
@@ -15724,7 +15724,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="547" ht="16" customHeight="1">
+    <row r="547" ht="18" customHeight="1">
       <c r="A547" s="3" t="n">
         <v>2025</v>
       </c>
@@ -15753,7 +15753,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="548" ht="16" customHeight="1">
+    <row r="548" ht="18" customHeight="1">
       <c r="A548" s="3" t="n">
         <v>2024</v>
       </c>
@@ -15776,7 +15776,7 @@
         <v>45.9</v>
       </c>
     </row>
-    <row r="549" ht="16" customHeight="1">
+    <row r="549" ht="18" customHeight="1">
       <c r="A549" s="3" t="n">
         <v>2025</v>
       </c>
@@ -15799,7 +15799,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="550" ht="16" customHeight="1">
+    <row r="550" ht="18" customHeight="1">
       <c r="A550" s="3" t="n">
         <v>2024</v>
       </c>
@@ -15819,7 +15819,7 @@
         <v>38.8</v>
       </c>
     </row>
-    <row r="551" ht="16" customHeight="1">
+    <row r="551" ht="18" customHeight="1">
       <c r="A551" s="3" t="n">
         <v>2025</v>
       </c>
@@ -15842,7 +15842,7 @@
         <v>43.9</v>
       </c>
     </row>
-    <row r="552" ht="16" customHeight="1">
+    <row r="552" ht="18" customHeight="1">
       <c r="A552" s="3" t="n">
         <v>2024</v>
       </c>
@@ -15865,7 +15865,7 @@
         <v>39.6</v>
       </c>
     </row>
-    <row r="553" ht="16" customHeight="1">
+    <row r="553" ht="18" customHeight="1">
       <c r="A553" s="3" t="n">
         <v>2025</v>
       </c>
@@ -15888,7 +15888,7 @@
         <v>45.6</v>
       </c>
     </row>
-    <row r="554" ht="16" customHeight="1">
+    <row r="554" ht="18" customHeight="1">
       <c r="A554" s="3" t="n">
         <v>2024</v>
       </c>
@@ -15908,7 +15908,7 @@
         <v>40.1</v>
       </c>
     </row>
-    <row r="555" ht="16" customHeight="1">
+    <row r="555" ht="18" customHeight="1">
       <c r="A555" s="3" t="n">
         <v>2025</v>
       </c>
@@ -15931,7 +15931,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="556" ht="16" customHeight="1">
+    <row r="556" ht="18" customHeight="1">
       <c r="A556" s="3" t="n">
         <v>2024</v>
       </c>
@@ -15957,7 +15957,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="557" ht="16" customHeight="1">
+    <row r="557" ht="18" customHeight="1">
       <c r="A557" s="3" t="n">
         <v>2025</v>
       </c>
@@ -15983,7 +15983,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="558" ht="16" customHeight="1">
+    <row r="558" ht="18" customHeight="1">
       <c r="A558" s="3" t="n">
         <v>2024</v>
       </c>
@@ -16006,7 +16006,7 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="559" ht="16" customHeight="1">
+    <row r="559" ht="18" customHeight="1">
       <c r="A559" s="3" t="n">
         <v>2025</v>
       </c>
@@ -16032,7 +16032,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="560" ht="16" customHeight="1">
+    <row r="560" ht="18" customHeight="1">
       <c r="A560" s="3" t="n">
         <v>2024</v>
       </c>
@@ -16055,7 +16055,7 @@
         <v>36.2</v>
       </c>
     </row>
-    <row r="561" ht="16" customHeight="1">
+    <row r="561" ht="18" customHeight="1">
       <c r="A561" s="3" t="n">
         <v>2025</v>
       </c>
@@ -16081,7 +16081,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="562" ht="16" customHeight="1">
+    <row r="562" ht="18" customHeight="1">
       <c r="A562" s="3" t="n">
         <v>2024</v>
       </c>
@@ -16104,7 +16104,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="563" ht="16" customHeight="1">
+    <row r="563" ht="18" customHeight="1">
       <c r="A563" s="3" t="n">
         <v>2025</v>
       </c>
@@ -16127,7 +16127,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="564" ht="16" customHeight="1">
+    <row r="564" ht="18" customHeight="1">
       <c r="A564" s="3" t="n">
         <v>2024</v>
       </c>
@@ -16150,7 +16150,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="565" ht="16" customHeight="1">
+    <row r="565" ht="18" customHeight="1">
       <c r="A565" s="3" t="n">
         <v>2025</v>
       </c>
@@ -16173,7 +16173,7 @@
         <v>48.2</v>
       </c>
     </row>
-    <row r="566" ht="16" customHeight="1">
+    <row r="566" ht="18" customHeight="1">
       <c r="A566" s="3" t="n">
         <v>2024</v>
       </c>
@@ -16196,7 +16196,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="567" ht="16" customHeight="1">
+    <row r="567" ht="18" customHeight="1">
       <c r="A567" s="3" t="n">
         <v>2025</v>
       </c>
@@ -16216,7 +16216,7 @@
         <v>116.3</v>
       </c>
     </row>
-    <row r="568" ht="16" customHeight="1">
+    <row r="568" ht="18" customHeight="1">
       <c r="A568" s="3" t="n">
         <v>2024</v>
       </c>
@@ -16239,7 +16239,7 @@
         <v>43.6</v>
       </c>
     </row>
-    <row r="569" ht="16" customHeight="1">
+    <row r="569" ht="18" customHeight="1">
       <c r="A569" s="3" t="n">
         <v>2025</v>
       </c>
@@ -16262,7 +16262,7 @@
         <v>42.1</v>
       </c>
     </row>
-    <row r="570" ht="16" customHeight="1">
+    <row r="570" ht="18" customHeight="1">
       <c r="A570" s="3" t="n">
         <v>2024</v>
       </c>
@@ -16285,7 +16285,7 @@
         <v>35.9</v>
       </c>
     </row>
-    <row r="571" ht="16" customHeight="1">
+    <row r="571" ht="18" customHeight="1">
       <c r="A571" s="3" t="n">
         <v>2025</v>
       </c>
@@ -16308,7 +16308,7 @@
         <v>34.3</v>
       </c>
     </row>
-    <row r="572" ht="16" customHeight="1">
+    <row r="572" ht="18" customHeight="1">
       <c r="A572" s="3" t="n">
         <v>2024</v>
       </c>
@@ -16331,7 +16331,7 @@
         <v>34.6</v>
       </c>
     </row>
-    <row r="573" ht="16" customHeight="1">
+    <row r="573" ht="18" customHeight="1">
       <c r="A573" s="3" t="n">
         <v>2025</v>
       </c>
@@ -16354,7 +16354,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="574" ht="16" customHeight="1">
+    <row r="574" ht="18" customHeight="1">
       <c r="A574" s="3" t="n">
         <v>2024</v>
       </c>
@@ -16377,7 +16377,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="575" ht="16" customHeight="1">
+    <row r="575" ht="18" customHeight="1">
       <c r="A575" s="3" t="n">
         <v>2025</v>
       </c>
@@ -16400,7 +16400,7 @@
         <v>28.6</v>
       </c>
     </row>
-    <row r="576" ht="16" customHeight="1">
+    <row r="576" ht="18" customHeight="1">
       <c r="A576" s="3" t="n">
         <v>2024</v>
       </c>
@@ -16423,7 +16423,7 @@
         <v>30.2</v>
       </c>
     </row>
-    <row r="577" ht="16" customHeight="1">
+    <row r="577" ht="18" customHeight="1">
       <c r="A577" s="3" t="n">
         <v>2025</v>
       </c>
@@ -16446,7 +16446,7 @@
         <v>36.7</v>
       </c>
     </row>
-    <row r="578" ht="16" customHeight="1">
+    <row r="578" ht="18" customHeight="1">
       <c r="A578" s="3" t="n">
         <v>2024</v>
       </c>
@@ -16469,7 +16469,7 @@
         <v>30.9</v>
       </c>
     </row>
-    <row r="579" ht="16" customHeight="1">
+    <row r="579" ht="18" customHeight="1">
       <c r="A579" s="3" t="n">
         <v>2025</v>
       </c>
@@ -16492,7 +16492,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="580" ht="16" customHeight="1">
+    <row r="580" ht="18" customHeight="1">
       <c r="A580" s="3" t="n">
         <v>2024</v>
       </c>
@@ -16515,7 +16515,7 @@
         <v>33.2</v>
       </c>
     </row>
-    <row r="581" ht="16" customHeight="1">
+    <row r="581" ht="18" customHeight="1">
       <c r="A581" s="3" t="n">
         <v>2025</v>
       </c>
@@ -16538,7 +16538,7 @@
         <v>37.2</v>
       </c>
     </row>
-    <row r="582" ht="16" customHeight="1">
+    <row r="582" ht="18" customHeight="1">
       <c r="A582" s="3" t="n">
         <v>2024</v>
       </c>
@@ -16561,7 +16561,7 @@
         <v>42.4</v>
       </c>
     </row>
-    <row r="583" ht="16" customHeight="1">
+    <row r="583" ht="18" customHeight="1">
       <c r="A583" s="3" t="n">
         <v>2025</v>
       </c>
@@ -16584,7 +16584,7 @@
         <v>47.6</v>
       </c>
     </row>
-    <row r="584" ht="16" customHeight="1">
+    <row r="584" ht="18" customHeight="1">
       <c r="A584" s="3" t="n">
         <v>2024</v>
       </c>
@@ -16598,7 +16598,7 @@
         <v>30.9</v>
       </c>
     </row>
-    <row r="585" ht="16" customHeight="1">
+    <row r="585" ht="18" customHeight="1">
       <c r="A585" s="3" t="n">
         <v>2025</v>
       </c>
@@ -16615,7 +16615,7 @@
         <v>60.6</v>
       </c>
     </row>
-    <row r="586" ht="16" customHeight="1">
+    <row r="586" ht="18" customHeight="1">
       <c r="A586" s="3" t="n">
         <v>2024</v>
       </c>
@@ -16635,7 +16635,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="587" ht="16" customHeight="1">
+    <row r="587" ht="18" customHeight="1">
       <c r="A587" s="3" t="n">
         <v>2025</v>
       </c>
@@ -16658,7 +16658,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="588" ht="16" customHeight="1">
+    <row r="588" ht="18" customHeight="1">
       <c r="A588" s="3" t="n">
         <v>2024</v>
       </c>
@@ -16681,7 +16681,7 @@
         <v>35.7</v>
       </c>
     </row>
-    <row r="589" ht="16" customHeight="1">
+    <row r="589" ht="18" customHeight="1">
       <c r="A589" s="3" t="n">
         <v>2025</v>
       </c>
@@ -16704,7 +16704,7 @@
         <v>34.4</v>
       </c>
     </row>
-    <row r="590" ht="16" customHeight="1">
+    <row r="590" ht="18" customHeight="1">
       <c r="A590" s="3" t="n">
         <v>2024</v>
       </c>
@@ -16724,7 +16724,7 @@
         <v>73.2</v>
       </c>
     </row>
-    <row r="591" ht="16" customHeight="1">
+    <row r="591" ht="18" customHeight="1">
       <c r="A591" s="3" t="n">
         <v>2025</v>
       </c>
